--- a/Test/Test Suite/TestPlanPrincipleService.xlsx
+++ b/Test/Test Suite/TestPlanPrincipleService.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" tabRatio="600" firstSheet="12" activeTab="12" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="2328" windowWidth="17280" windowHeight="9420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
@@ -27,8 +27,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="8">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -50,28 +52,12 @@
       <sz val="14"/>
     </font>
     <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="TH Sarabun New"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="16"/>
-    </font>
-    <font>
       <name val="TH Sarabun New"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Aptos Narrow"/>
       <sz val="14"/>
-    </font>
-    <font>
-      <name val="TH Sarabun New"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -94,7 +80,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -109,19 +95,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -152,30 +125,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -214,36 +163,23 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -266,6 +202,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -277,11 +237,20 @@
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -305,49 +274,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -356,108 +287,89 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -855,15 +767,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="21.77734375" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
     <col width="25.5546875" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
     <col width="18.109375" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
     <col width="8.88671875" customWidth="1" style="2" min="4" max="5"/>
-    <col width="22" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
-    <col width="8.88671875" customWidth="1" style="2" min="7" max="7"/>
+    <col width="66.21875" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
+    <col width="26.44140625" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -921,672 +833,920 @@
           <t>Relative Defects (ID)</t>
         </is>
       </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Line Coverage (%)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="42" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>ArmyService</t>
         </is>
       </c>
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>sendArmy</t>
         </is>
       </c>
-      <c r="C6" s="42" t="n">
+      <c r="C6" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="D6" s="42" t="n"/>
-      <c r="E6" s="42" t="n"/>
-      <c r="F6" s="42" t="n"/>
+      <c r="D6" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="23" t="n"/>
+      <c r="G6" s="22" t="n">
+        <v>95.12</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>ArmyService</t>
         </is>
       </c>
-      <c r="B7" s="42" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>cancelIfDestroyed</t>
         </is>
       </c>
-      <c r="C7" s="42" t="n">
+      <c r="C7" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="42" t="n"/>
-      <c r="E7" s="42" t="n"/>
-      <c r="F7" s="42" t="n"/>
+      <c r="D7" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="23" t="n"/>
+      <c r="G7" s="39" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="42" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>ArmyService</t>
         </is>
       </c>
-      <c r="B8" s="42" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>findDueArmies</t>
         </is>
       </c>
-      <c r="C8" s="42" t="n">
+      <c r="C8" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="42" t="n"/>
-      <c r="E8" s="42" t="n"/>
-      <c r="F8" s="42" t="n"/>
+      <c r="D8" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="39" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="42" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>ArmyService</t>
         </is>
       </c>
-      <c r="B9" s="42" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>findByOwner</t>
         </is>
       </c>
-      <c r="C9" s="42" t="n">
+      <c r="C9" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="42" t="n"/>
-      <c r="E9" s="42" t="n"/>
-      <c r="F9" s="42" t="n"/>
+      <c r="D9" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="23" t="n"/>
+      <c r="G9" s="39" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="42" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>ArmyService</t>
         </is>
       </c>
-      <c r="B10" s="42" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>findById</t>
         </is>
       </c>
-      <c r="C10" s="42" t="n">
+      <c r="C10" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="42" t="n"/>
-      <c r="E10" s="42" t="n"/>
-      <c r="F10" s="42" t="n"/>
+      <c r="D10" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="40" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="42" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>BattleService</t>
         </is>
       </c>
-      <c r="B11" s="42" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>resolveBattles</t>
         </is>
       </c>
-      <c r="C11" s="42" t="n">
+      <c r="C11" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="42" t="n"/>
-      <c r="E11" s="42" t="n"/>
-      <c r="F11" s="42" t="n"/>
+      <c r="D11" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>DEF-SVC-01</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="n">
+        <v>93.86</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="42" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>BattleService</t>
         </is>
       </c>
-      <c r="B12" s="42" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>findById</t>
         </is>
       </c>
-      <c r="C12" s="42" t="n">
+      <c r="C12" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="42" t="n"/>
-      <c r="E12" s="42" t="n"/>
-      <c r="F12" s="42" t="n"/>
+      <c r="D12" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="23" t="n"/>
+      <c r="G12" s="40" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="42" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>CityService</t>
         </is>
       </c>
-      <c r="B13" s="42" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>produceFood</t>
         </is>
       </c>
-      <c r="C13" s="42" t="n">
+      <c r="C13" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="42" t="n"/>
-      <c r="E13" s="42" t="n"/>
-      <c r="F13" s="42" t="n"/>
+      <c r="D13" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="22" t="n">
+        <v>90.06</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="42" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>CityService</t>
         </is>
       </c>
-      <c r="B14" s="42" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>recruitSoldiers</t>
         </is>
       </c>
-      <c r="C14" s="42" t="n">
+      <c r="C14" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="42" t="n"/>
-      <c r="E14" s="42" t="n"/>
-      <c r="F14" s="42" t="n"/>
+      <c r="D14" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="23" t="n"/>
+      <c r="G14" s="39" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="42" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>CityService</t>
         </is>
       </c>
-      <c r="B15" s="42" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>getConnectedNetwork</t>
         </is>
       </c>
-      <c r="C15" s="42" t="n">
+      <c r="C15" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="42" t="n"/>
-      <c r="E15" s="42" t="n"/>
-      <c r="F15" s="42" t="n"/>
+      <c r="D15" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="39" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="42" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>CityService</t>
         </is>
       </c>
-      <c r="B16" s="42" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>findById</t>
         </is>
       </c>
-      <c r="C16" s="42" t="n">
+      <c r="C16" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="42" t="n"/>
-      <c r="E16" s="42" t="n"/>
-      <c r="F16" s="42" t="n"/>
+      <c r="D16" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="23" t="n"/>
+      <c r="G16" s="39" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="42" t="inlineStr">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>CityService</t>
         </is>
       </c>
-      <c r="B17" s="42" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>save</t>
         </is>
       </c>
-      <c r="C17" s="42" t="n">
+      <c r="C17" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="42" t="n"/>
-      <c r="E17" s="42" t="n"/>
-      <c r="F17" s="42" t="n"/>
+      <c r="D17" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="23" t="n"/>
+      <c r="G17" s="39" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="42" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>CityService</t>
         </is>
       </c>
-      <c r="B18" s="42" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>deductFoodFromNetwork</t>
         </is>
       </c>
-      <c r="C18" s="42" t="n">
+      <c r="C18" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="42" t="n"/>
-      <c r="E18" s="42" t="n"/>
-      <c r="F18" s="42" t="n"/>
+      <c r="D18" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>DEF-SVC-02</t>
+        </is>
+      </c>
+      <c r="G18" s="39" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>CityService</t>
         </is>
       </c>
-      <c r="B19" s="42" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>applySeasonUpkeep</t>
         </is>
       </c>
-      <c r="C19" s="42" t="n">
+      <c r="C19" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="D19" s="42" t="n"/>
-      <c r="E19" s="42" t="n"/>
-      <c r="F19" s="42" t="n"/>
+      <c r="D19" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="E19" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>DEF-SVC-03, DEF-SVC-04</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="42" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>GameClock</t>
         </is>
       </c>
-      <c r="B20" s="42" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="C20" s="42" t="n">
+      <c r="C20" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="42" t="n"/>
-      <c r="E20" s="42" t="n"/>
-      <c r="F20" s="42" t="n"/>
+      <c r="D20" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="23" t="n"/>
+      <c r="G20" s="22" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="42" t="inlineStr">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>GameClock</t>
         </is>
       </c>
-      <c r="B21" s="42" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>isDaytime</t>
         </is>
       </c>
-      <c r="C21" s="42" t="n">
+      <c r="C21" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="42" t="n"/>
-      <c r="E21" s="42" t="n"/>
-      <c r="F21" s="42" t="n"/>
+      <c r="D21" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="39" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="42" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>GameClock</t>
         </is>
       </c>
-      <c r="B22" s="42" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>isSeasonEnd</t>
         </is>
       </c>
-      <c r="C22" s="42" t="n">
+      <c r="C22" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="42" t="n"/>
-      <c r="E22" s="42" t="n"/>
-      <c r="F22" s="42" t="n"/>
+      <c r="D22" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="23" t="n"/>
+      <c r="G22" s="40" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="42" t="inlineStr">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>GameRuleService</t>
         </is>
       </c>
-      <c r="B23" s="42" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>checkPlayerElimination</t>
         </is>
       </c>
-      <c r="C23" s="42" t="n">
+      <c r="C23" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="42" t="n"/>
-      <c r="E23" s="42" t="n"/>
-      <c r="F23" s="42" t="n"/>
+      <c r="D23" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="23" t="n"/>
+      <c r="G23" s="22" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="42" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>GameRuleService</t>
         </is>
       </c>
-      <c r="B24" s="42" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>checkWinCondition</t>
         </is>
       </c>
-      <c r="C24" s="42" t="n">
+      <c r="C24" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="D24" s="42" t="n"/>
-      <c r="E24" s="42" t="n"/>
-      <c r="F24" s="42" t="n"/>
+      <c r="D24" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="23" t="n"/>
+      <c r="G24" s="40" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="42" t="inlineStr">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>GameService</t>
         </is>
       </c>
-      <c r="B25" s="42" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>createGame</t>
         </is>
       </c>
-      <c r="C25" s="42" t="n">
+      <c r="C25" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="42" t="n"/>
-      <c r="E25" s="42" t="n"/>
-      <c r="F25" s="42" t="n"/>
+      <c r="D25" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="23" t="n"/>
+      <c r="G25" s="22" t="n">
+        <v>84.44</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="42" t="inlineStr">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>GameService</t>
         </is>
       </c>
-      <c r="B26" s="42" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>addPlayer</t>
         </is>
       </c>
-      <c r="C26" s="42" t="n">
+      <c r="C26" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="D26" s="42" t="n"/>
-      <c r="E26" s="42" t="n"/>
-      <c r="F26" s="42" t="n"/>
+      <c r="D26" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="23" t="n"/>
+      <c r="G26" s="39" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="42" t="inlineStr">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>GameService</t>
         </is>
       </c>
-      <c r="B27" s="42" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>startGame</t>
         </is>
       </c>
-      <c r="C27" s="42" t="n">
+      <c r="C27" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="D27" s="42" t="n"/>
-      <c r="E27" s="42" t="n"/>
-      <c r="F27" s="42" t="n"/>
+      <c r="D27" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="23" t="n"/>
+      <c r="G27" s="39" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="42" t="inlineStr">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>GameService</t>
         </is>
       </c>
-      <c r="B28" s="42" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>findByRoomCode</t>
         </is>
       </c>
-      <c r="C28" s="42" t="n">
+      <c r="C28" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="42" t="n"/>
-      <c r="E28" s="42" t="n"/>
-      <c r="F28" s="42" t="n"/>
+      <c r="D28" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="23" t="n"/>
+      <c r="G28" s="39" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="42" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>GameService</t>
         </is>
       </c>
-      <c r="B29" s="42" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>findPlayers</t>
         </is>
       </c>
-      <c r="C29" s="42" t="n">
+      <c r="C29" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="42" t="n"/>
-      <c r="E29" s="42" t="n"/>
-      <c r="F29" s="42" t="n"/>
+      <c r="D29" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="23" t="n"/>
+      <c r="G29" s="40" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="42" t="inlineStr">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t>MarshalDraftService</t>
         </is>
       </c>
-      <c r="B30" s="42" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>prepareNextPlayer</t>
         </is>
       </c>
-      <c r="C30" s="42" t="n">
+      <c r="C30" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="D30" s="42" t="n"/>
-      <c r="E30" s="42" t="n"/>
-      <c r="F30" s="42" t="n"/>
+      <c r="D30" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>DEF-SVC-05</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="42" t="inlineStr">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>MarshalDraftService</t>
         </is>
       </c>
-      <c r="B31" s="42" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>reroll</t>
         </is>
       </c>
-      <c r="C31" s="42" t="n">
+      <c r="C31" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="D31" s="42" t="n"/>
-      <c r="E31" s="42" t="n"/>
-      <c r="F31" s="42" t="n"/>
+      <c r="D31" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="23" t="n"/>
+      <c r="G31" s="39" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="42" t="inlineStr">
+      <c r="A32" s="23" t="inlineStr">
         <is>
           <t>MarshalDraftService</t>
         </is>
       </c>
-      <c r="B32" s="42" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>selectCurrentCandidate</t>
         </is>
       </c>
-      <c r="C32" s="42" t="n">
+      <c r="C32" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="D32" s="42" t="n"/>
-      <c r="E32" s="42" t="n"/>
-      <c r="F32" s="42" t="n"/>
+      <c r="D32" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="23" t="n"/>
+      <c r="G32" s="40" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="42" t="inlineStr">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>PlacementService</t>
         </is>
       </c>
-      <c r="B33" s="42" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>selectBase</t>
         </is>
       </c>
-      <c r="C33" s="42" t="n">
+      <c r="C33" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="D33" s="42" t="n"/>
-      <c r="E33" s="42" t="n"/>
-      <c r="F33" s="42" t="n"/>
+      <c r="D33" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="E33" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>DEF-SVC-06</t>
+        </is>
+      </c>
+      <c r="G33" s="37" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="42" t="inlineStr">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>PlayerService</t>
         </is>
       </c>
-      <c r="B34" s="42" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>findById</t>
         </is>
       </c>
-      <c r="C34" s="42" t="n">
+      <c r="C34" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="D34" s="42" t="n"/>
-      <c r="E34" s="42" t="n"/>
-      <c r="F34" s="42" t="n"/>
+      <c r="D34" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="23" t="n"/>
+      <c r="G34" s="22" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="42" t="inlineStr">
+      <c r="A35" s="23" t="inlineStr">
         <is>
           <t>PlayerService</t>
         </is>
       </c>
-      <c r="B35" s="42" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>getAlivePlayerValidated</t>
         </is>
       </c>
-      <c r="C35" s="42" t="n">
+      <c r="C35" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="D35" s="42" t="n"/>
-      <c r="E35" s="42" t="n"/>
-      <c r="F35" s="42" t="n"/>
+      <c r="D35" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="23" t="n"/>
+      <c r="G35" s="39" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="42" t="inlineStr">
+      <c r="A36" s="23" t="inlineStr">
         <is>
           <t>PlayerService</t>
         </is>
       </c>
-      <c r="B36" s="42" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>findByGame</t>
         </is>
       </c>
-      <c r="C36" s="42" t="n">
+      <c r="C36" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="42" t="n"/>
-      <c r="E36" s="42" t="n"/>
-      <c r="F36" s="42" t="n"/>
+      <c r="D36" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="23" t="n"/>
+      <c r="G36" s="39" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="42" t="inlineStr">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>PlayerService</t>
         </is>
       </c>
-      <c r="B37" s="42" t="inlineStr">
+      <c r="B37" s="23" t="inlineStr">
         <is>
           <t>findAliveByGame</t>
         </is>
       </c>
-      <c r="C37" s="42" t="n">
+      <c r="C37" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="42" t="n"/>
-      <c r="E37" s="42" t="n"/>
-      <c r="F37" s="42" t="n"/>
+      <c r="D37" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="23" t="n"/>
+      <c r="G37" s="40" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="42" t="inlineStr">
+      <c r="A38" s="23" t="inlineStr">
         <is>
           <t>TurnActionService</t>
         </is>
       </c>
-      <c r="B38" s="42" t="inlineStr">
+      <c r="B38" s="23" t="inlineStr">
         <is>
           <t>performAction</t>
         </is>
       </c>
-      <c r="C38" s="42" t="n">
+      <c r="C38" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="D38" s="42" t="n"/>
-      <c r="E38" s="42" t="n"/>
-      <c r="F38" s="42" t="n"/>
+      <c r="D38" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="E38" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="23" t="n"/>
+      <c r="G38" s="22" t="n">
+        <v>92.31</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="42" t="inlineStr">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t>TurnActionService</t>
         </is>
       </c>
-      <c r="B39" s="42" t="inlineStr">
+      <c r="B39" s="23" t="inlineStr">
         <is>
           <t>findTurnActions</t>
         </is>
       </c>
-      <c r="C39" s="42" t="n">
+      <c r="C39" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="42" t="n"/>
-      <c r="E39" s="42" t="n"/>
-      <c r="F39" s="42" t="n"/>
+      <c r="D39" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="23" t="n"/>
+      <c r="G39" s="40" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="42" t="inlineStr">
+      <c r="A40" s="23" t="inlineStr">
         <is>
           <t>TurnService</t>
         </is>
       </c>
-      <c r="B40" s="42" t="inlineStr">
+      <c r="B40" s="23" t="inlineStr">
         <is>
           <t>resolveAndAdvance</t>
         </is>
       </c>
-      <c r="C40" s="42" t="n">
+      <c r="C40" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="D40" s="42" t="n"/>
-      <c r="E40" s="42" t="n"/>
-      <c r="F40" s="42" t="n"/>
+      <c r="D40" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="E40" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="23" t="n"/>
+      <c r="G40" s="22" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="42" t="inlineStr">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>TurnService</t>
         </is>
       </c>
-      <c r="B41" s="42" t="inlineStr">
+      <c r="B41" s="23" t="inlineStr">
         <is>
           <t>getCurrentGame</t>
         </is>
       </c>
-      <c r="C41" s="42" t="n">
+      <c r="C41" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="42" t="n"/>
-      <c r="E41" s="42" t="n"/>
-      <c r="F41" s="42" t="n"/>
+      <c r="D41" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="23" t="n"/>
+      <c r="G41" s="40" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="42" t="inlineStr">
+      <c r="A42" s="23" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B42" s="49" t="n"/>
-      <c r="C42" s="42" t="n">
+      <c r="B42" s="24" t="n"/>
+      <c r="C42" s="23" t="n">
         <v>147</v>
       </c>
-      <c r="D42" s="44" t="n"/>
-      <c r="E42" s="44" t="n"/>
-      <c r="F42" s="44" t="n"/>
+      <c r="D42" s="15" t="n">
+        <v>142</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>DEF-SVC-01, DEF-SVC-02, DEF-SVC-03, DEF-SVC-04, DEF-SVC-05, DEF-SVC-06</t>
+        </is>
+      </c>
+      <c r="G42" s="38" t="n">
+        <v>93.03</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="11">
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="G6:G10"/>
+    <mergeCell ref="G13:G19"/>
     <mergeCell ref="A42:B42"/>
+    <mergeCell ref="G25:G29"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G34:G37"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="G40:G41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1604,381 +1764,464 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="4"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Project Name</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="33" t="n"/>
-      <c r="D3" s="33" t="n"/>
-      <c r="E3" s="33" t="n"/>
-      <c r="F3" s="33" t="n"/>
-      <c r="G3" s="34" t="n"/>
+      <c r="C3" s="32" t="n"/>
+      <c r="D3" s="32" t="n"/>
+      <c r="E3" s="32" t="n"/>
+      <c r="F3" s="32" t="n"/>
+      <c r="G3" s="24" t="n"/>
     </row>
     <row r="4" ht="84" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>SystemUnderTest/Class under Test</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>PlacementService</t>
         </is>
       </c>
-      <c r="C4" s="33" t="n"/>
-      <c r="D4" s="33" t="n"/>
-      <c r="E4" s="33" t="n"/>
-      <c r="F4" s="33" t="n"/>
-      <c r="G4" s="34" t="n"/>
+      <c r="C4" s="32" t="n"/>
+      <c r="D4" s="32" t="n"/>
+      <c r="E4" s="32" t="n"/>
+      <c r="F4" s="32" t="n"/>
+      <c r="G4" s="24" t="n"/>
     </row>
     <row r="5" ht="35.4" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
-        <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
-        </is>
-      </c>
-      <c r="C5" s="33" t="n"/>
-      <c r="D5" s="33" t="n"/>
-      <c r="E5" s="33" t="n"/>
-      <c r="F5" s="33" t="n"/>
-      <c r="G5" s="34" t="n"/>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6" ht="21" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
+      <c r="B6" s="34" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="33" t="n"/>
-      <c r="D6" s="33" t="n"/>
-      <c r="E6" s="33" t="n"/>
-      <c r="F6" s="33" t="n"/>
-      <c r="G6" s="34" t="n"/>
+      <c r="C6" s="32" t="n"/>
+      <c r="D6" s="32" t="n"/>
+      <c r="E6" s="32" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="24" t="n"/>
     </row>
     <row r="7" ht="35.4" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Mock GameRepository, PlayerRepository, CityRepository</t>
         </is>
       </c>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="33" t="n"/>
-      <c r="E7" s="33" t="n"/>
-      <c r="F7" s="33" t="n"/>
-      <c r="G7" s="34" t="n"/>
+      <c r="C7" s="32" t="n"/>
+      <c r="D7" s="32" t="n"/>
+      <c r="E7" s="32" t="n"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="24" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="46" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>TestCaseID</t>
         </is>
       </c>
-      <c r="B11" s="46" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>Function Under Test</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>TestData</t>
         </is>
       </c>
-      <c r="D11" s="46" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="E11" s="46" t="inlineStr">
+      <c r="E11" s="31" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F11" s="46" t="inlineStr">
+      <c r="F11" s="31" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G11" s="46" t="inlineStr">
+      <c r="G11" s="31" t="inlineStr">
         <is>
           <t>DefectID</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="63" customHeight="1">
-      <c r="A12" s="46" t="inlineStr">
+    <row r="12" ht="108" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>TC01</t>
         </is>
       </c>
-      <c r="B12" s="46" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>selectBase</t>
         </is>
       </c>
-      <c r="C12" s="47" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>P1 -&gt; City1 and P2 -&gt; City2 (distinct cities), last selection triggers resolve</t>
         </is>
       </c>
-      <c r="D12" s="47" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>City1.player = P1, name "P1's &lt;name&gt;", soldiers 0, food 50; same for City2/P2; both startingCityId reset to null; game.status = IN_PROGRESS, currentTurnNumber = 1; game saved</t>
         </is>
       </c>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>City1 owned by P1 and renamed "Player1's City1" with 0 soldiers and 50 food, City2 owned by P2 and renamed "Player2's City2"; both startingCityId reset to null; game IN_PROGRESS with currentTurnNumber 1 and saved</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G12" s="31" t="n"/>
     </row>
     <row r="13" ht="84" customHeight="1">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>TC02</t>
         </is>
       </c>
-      <c r="B13" s="46" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>selectBase</t>
         </is>
       </c>
-      <c r="C13" s="47" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>P1.selectBase(1L,1L,1L) then P2.selectBase(1L,1L,1L) - both choose City1</t>
         </is>
       </c>
-      <c r="D13" s="47" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>conflict -&gt; every player's startingCityId reset to null, playerRepository.saveAll called, game stays in PLACEMENT</t>
         </is>
       </c>
-      <c r="E13" s="46" t="n"/>
-      <c r="F13" s="46" t="n"/>
-      <c r="G13" s="46" t="n"/>
-    </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="46" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>conflict path: both startingCityId reset to null, playerRepository.saveAll([P1,P2]) called, game still PLACEMENT and no city saved</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="n"/>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>TC03</t>
         </is>
       </c>
-      <c r="B14" s="46" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>selectBase</t>
         </is>
       </c>
-      <c r="C14" s="47" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>P1 selects City1 while P2 has not selected yet</t>
         </is>
       </c>
-      <c r="D14" s="47" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>P1.startingCityId == 1; no city ownership change; game still PLACEMENT</t>
         </is>
       </c>
-      <c r="E14" s="46" t="n"/>
-      <c r="F14" s="46" t="n"/>
-      <c r="G14" s="46" t="n"/>
-    </row>
-    <row r="15" ht="21" customHeight="1">
-      <c r="A15" s="46" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>waits for the other player: P1.startingCityId == 1, City1.player still null, game still PLACEMENT, no city saved</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G14" s="31" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>TC04</t>
         </is>
       </c>
-      <c r="B15" s="46" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>selectBase</t>
         </is>
       </c>
-      <c r="C15" s="47" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>game.status = IN_PROGRESS</t>
         </is>
       </c>
-      <c r="D15" s="47" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'Game is not in placement phase'</t>
         </is>
       </c>
-      <c r="E15" s="46" t="n"/>
-      <c r="F15" s="46" t="n"/>
-      <c r="G15" s="46" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="46" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'Game is not in placement phase'</t>
+        </is>
+      </c>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G15" s="31" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>TC05</t>
         </is>
       </c>
-      <c r="B16" s="46" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>selectBase</t>
         </is>
       </c>
-      <c r="C16" s="47" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>gameRepository.findByIdForUpdate(99L) empty</t>
         </is>
       </c>
-      <c r="D16" s="47" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>throws ResourceNotFoundException 'Game not found with id: 99'</t>
         </is>
       </c>
-      <c r="E16" s="46" t="n"/>
-      <c r="F16" s="46" t="n"/>
-      <c r="G16" s="46" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="46" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>ResourceNotFoundException 'Game not found with id: 99'</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G16" s="31" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>TC06</t>
         </is>
       </c>
-      <c r="B17" s="46" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>selectBase</t>
         </is>
       </c>
-      <c r="C17" s="47" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>playerId belongs to another game</t>
         </is>
       </c>
-      <c r="D17" s="47" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'Player does not belong to this game'</t>
         </is>
       </c>
-      <c r="E17" s="46" t="n"/>
-      <c r="F17" s="46" t="n"/>
-      <c r="G17" s="46" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="46" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'Player does not belong to this game'</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>TC07</t>
         </is>
       </c>
-      <c r="B18" s="46" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>selectBase</t>
         </is>
       </c>
-      <c r="C18" s="47" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>playerRepository.findById(99L) empty</t>
         </is>
       </c>
-      <c r="D18" s="47" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>throws ResourceNotFoundException 'Player not found with id: 99'</t>
         </is>
       </c>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="46" t="n"/>
-      <c r="G18" s="46" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="46" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>ResourceNotFoundException 'Player not found with id: 99'</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>TC08</t>
         </is>
       </c>
-      <c r="B19" s="46" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>selectBase</t>
         </is>
       </c>
-      <c r="C19" s="47" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>cityId belongs to another game</t>
         </is>
       </c>
-      <c r="D19" s="47" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'City does not belong to this game'</t>
         </is>
       </c>
-      <c r="E19" s="46" t="n"/>
-      <c r="F19" s="46" t="n"/>
-      <c r="G19" s="46" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="46" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'City does not belong to this game'</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>TC09</t>
         </is>
       </c>
-      <c r="B20" s="46" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>selectBase</t>
         </is>
       </c>
-      <c r="C20" s="47" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>cityRepository.findById(99L) empty</t>
         </is>
       </c>
-      <c r="D20" s="47" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>throws ResourceNotFoundException 'City not found with id: 99'</t>
         </is>
       </c>
-      <c r="E20" s="46" t="n"/>
-      <c r="F20" s="46" t="n"/>
-      <c r="G20" s="46" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="46" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>ResourceNotFoundException 'City not found with id: 99'</t>
+        </is>
+      </c>
+      <c r="F20" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>TC10</t>
         </is>
       </c>
-      <c r="B21" s="46" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>selectBase</t>
         </is>
       </c>
-      <c r="C21" s="47" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>playerRepository has no players for the game (empty list)</t>
         </is>
       </c>
-      <c r="D21" s="47" t="inlineStr">
+      <c r="D21" s="33" t="inlineStr">
         <is>
           <t>allMatch on an empty stream is true -&gt; resolution runs with zero players, game never advances</t>
         </is>
       </c>
-      <c r="E21" s="46" t="n"/>
-      <c r="F21" s="46" t="n"/>
-      <c r="G21" s="46" t="n"/>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>the game DOES advance: an empty roster has no conflict, so status becomes IN_PROGRESS with currentTurnNumber 1, playerRepository.saveAll([]) runs and no city gets an owner</t>
+        </is>
+      </c>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G21" s="31" t="inlineStr">
+        <is>
+          <t>DEF-SVC-06</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2004,306 +2247,361 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="4"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Project Name</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="33" t="n"/>
-      <c r="D3" s="33" t="n"/>
-      <c r="E3" s="33" t="n"/>
-      <c r="F3" s="33" t="n"/>
-      <c r="G3" s="34" t="n"/>
+      <c r="C3" s="32" t="n"/>
+      <c r="D3" s="32" t="n"/>
+      <c r="E3" s="32" t="n"/>
+      <c r="F3" s="32" t="n"/>
+      <c r="G3" s="24" t="n"/>
     </row>
     <row r="4" ht="84" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>SystemUnderTest/Class under Test</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>PlayerService</t>
         </is>
       </c>
-      <c r="C4" s="33" t="n"/>
-      <c r="D4" s="33" t="n"/>
-      <c r="E4" s="33" t="n"/>
-      <c r="F4" s="33" t="n"/>
-      <c r="G4" s="34" t="n"/>
+      <c r="C4" s="32" t="n"/>
+      <c r="D4" s="32" t="n"/>
+      <c r="E4" s="32" t="n"/>
+      <c r="F4" s="32" t="n"/>
+      <c r="G4" s="24" t="n"/>
     </row>
     <row r="5" ht="35.4" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
-        <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
-        </is>
-      </c>
-      <c r="C5" s="33" t="n"/>
-      <c r="D5" s="33" t="n"/>
-      <c r="E5" s="33" t="n"/>
-      <c r="F5" s="33" t="n"/>
-      <c r="G5" s="34" t="n"/>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6" ht="21" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
+      <c r="B6" s="34" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="33" t="n"/>
-      <c r="D6" s="33" t="n"/>
-      <c r="E6" s="33" t="n"/>
-      <c r="F6" s="33" t="n"/>
-      <c r="G6" s="34" t="n"/>
+      <c r="C6" s="32" t="n"/>
+      <c r="D6" s="32" t="n"/>
+      <c r="E6" s="32" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="24" t="n"/>
     </row>
     <row r="7" ht="35.4" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Mock PlayerRepository</t>
         </is>
       </c>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="33" t="n"/>
-      <c r="E7" s="33" t="n"/>
-      <c r="F7" s="33" t="n"/>
-      <c r="G7" s="34" t="n"/>
+      <c r="C7" s="32" t="n"/>
+      <c r="D7" s="32" t="n"/>
+      <c r="E7" s="32" t="n"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="24" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="46" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>TestCaseID</t>
         </is>
       </c>
-      <c r="B11" s="46" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>Function Under Test</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>TestData</t>
         </is>
       </c>
-      <c r="D11" s="46" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="E11" s="46" t="inlineStr">
+      <c r="E11" s="31" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F11" s="46" t="inlineStr">
+      <c r="F11" s="31" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G11" s="46" t="inlineStr">
+      <c r="G11" s="31" t="inlineStr">
         <is>
           <t>DefectID</t>
         </is>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
-      <c r="A12" s="46" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>TC01</t>
         </is>
       </c>
-      <c r="B12" s="46" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>findById</t>
         </is>
       </c>
-      <c r="C12" s="47" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>findById(1L), playerRepository = [Player(id1)]</t>
         </is>
       </c>
-      <c r="D12" s="47" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>player.getId() == 1L</t>
         </is>
       </c>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-    </row>
-    <row r="13" ht="21" customHeight="1">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>findById(1L).getId() == 1</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G12" s="31" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>TC02</t>
         </is>
       </c>
-      <c r="B13" s="46" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>findById</t>
         </is>
       </c>
-      <c r="C13" s="47" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>findById(2L), playerRepository = [Player(id1)]</t>
         </is>
       </c>
-      <c r="D13" s="47" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>Player not found with id: 2 (ResourceNotFoundException)</t>
         </is>
       </c>
-      <c r="E13" s="46" t="n"/>
-      <c r="F13" s="46" t="n"/>
-      <c r="G13" s="46" t="n"/>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>ResourceNotFoundException 'Player not found with id: 2'</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="n"/>
     </row>
     <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="46" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>TC03</t>
         </is>
       </c>
-      <c r="B14" s="46" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>getAlivePlayerValidated</t>
         </is>
       </c>
-      <c r="C14" s="47" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>getAlivePlayerValidated(1L), Player(id1, isAlive = true)</t>
         </is>
       </c>
-      <c r="D14" s="47" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>returns the player, getIsAlive() == true</t>
         </is>
       </c>
-      <c r="E14" s="46" t="n"/>
-      <c r="F14" s="46" t="n"/>
-      <c r="G14" s="46" t="n"/>
-    </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="46" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>the player is returned with getIsAlive() true</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G14" s="31" t="n"/>
+    </row>
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>TC04</t>
         </is>
       </c>
-      <c r="B15" s="46" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>getAlivePlayerValidated</t>
         </is>
       </c>
-      <c r="C15" s="47" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>getAlivePlayerValidated(99L), playerRepository = [Player(id1)]</t>
         </is>
       </c>
-      <c r="D15" s="47" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>Player not found with id: 99 (ResourceNotFoundException) - different from 'exists but eliminated'</t>
         </is>
       </c>
-      <c r="E15" s="46" t="n"/>
-      <c r="F15" s="46" t="n"/>
-      <c r="G15" s="46" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="46" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>ResourceNotFoundException 'Player not found with id: 99' (not the elimination message)</t>
+        </is>
+      </c>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G15" s="31" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>TC05</t>
         </is>
       </c>
-      <c r="B16" s="46" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>getAlivePlayerValidated</t>
         </is>
       </c>
-      <c r="C16" s="47" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>getAlivePlayerValidated(1L), Player(id1, isAlive = false)</t>
         </is>
       </c>
-      <c r="D16" s="47" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'Eliminated players cannot take actions'</t>
         </is>
       </c>
-      <c r="E16" s="46" t="n"/>
-      <c r="F16" s="46" t="n"/>
-      <c r="G16" s="46" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="46" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'Eliminated players cannot take actions'</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G16" s="31" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>TC06</t>
         </is>
       </c>
-      <c r="B17" s="46" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>findByGame</t>
         </is>
       </c>
-      <c r="C17" s="47" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>findByGame(1L), players [P1, P2, P3] in game 1</t>
         </is>
       </c>
-      <c r="D17" s="47" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>returns all 3 players ordered by id</t>
         </is>
       </c>
-      <c r="E17" s="46" t="n"/>
-      <c r="F17" s="46" t="n"/>
-      <c r="G17" s="46" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="46" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>findByGame(1L) returns all 3 players in id order</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>TC07</t>
         </is>
       </c>
-      <c r="B18" s="46" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>findAliveByGame</t>
         </is>
       </c>
-      <c r="C18" s="47" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>players [P1 alive, P2 eliminated, P3 alive] in game 1</t>
         </is>
       </c>
-      <c r="D18" s="47" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>returns [P1, P3] only</t>
         </is>
       </c>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="46" t="n"/>
-      <c r="G18" s="46" t="n"/>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>findAliveByGame(1L) returns 2 players (ids 1 and 3); the eliminated one is filtered out</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G18" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2329,431 +2627,526 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="4"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Project Name</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="33" t="n"/>
-      <c r="D3" s="33" t="n"/>
-      <c r="E3" s="33" t="n"/>
-      <c r="F3" s="33" t="n"/>
-      <c r="G3" s="34" t="n"/>
+      <c r="C3" s="32" t="n"/>
+      <c r="D3" s="32" t="n"/>
+      <c r="E3" s="32" t="n"/>
+      <c r="F3" s="32" t="n"/>
+      <c r="G3" s="24" t="n"/>
     </row>
     <row r="4" ht="84" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>SystemUnderTest/Class under Test</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>TurnActionService</t>
         </is>
       </c>
-      <c r="C4" s="33" t="n"/>
-      <c r="D4" s="33" t="n"/>
-      <c r="E4" s="33" t="n"/>
-      <c r="F4" s="33" t="n"/>
-      <c r="G4" s="34" t="n"/>
+      <c r="C4" s="32" t="n"/>
+      <c r="D4" s="32" t="n"/>
+      <c r="E4" s="32" t="n"/>
+      <c r="F4" s="32" t="n"/>
+      <c r="G4" s="24" t="n"/>
     </row>
     <row r="5" ht="35.4" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
-        <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
-        </is>
-      </c>
-      <c r="C5" s="33" t="n"/>
-      <c r="D5" s="33" t="n"/>
-      <c r="E5" s="33" t="n"/>
-      <c r="F5" s="33" t="n"/>
-      <c r="G5" s="34" t="n"/>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6" ht="21" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
+      <c r="B6" s="34" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="33" t="n"/>
-      <c r="D6" s="33" t="n"/>
-      <c r="E6" s="33" t="n"/>
-      <c r="F6" s="33" t="n"/>
-      <c r="G6" s="34" t="n"/>
+      <c r="C6" s="32" t="n"/>
+      <c r="D6" s="32" t="n"/>
+      <c r="E6" s="32" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="24" t="n"/>
     </row>
     <row r="7" ht="35.4" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Mock TurnActionRepository, GameRepository, PlayerService, CityRepository, CommandFactory</t>
         </is>
       </c>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="33" t="n"/>
-      <c r="E7" s="33" t="n"/>
-      <c r="F7" s="33" t="n"/>
-      <c r="G7" s="34" t="n"/>
+      <c r="C7" s="32" t="n"/>
+      <c r="D7" s="32" t="n"/>
+      <c r="E7" s="32" t="n"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="24" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="46" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>TestCaseID</t>
         </is>
       </c>
-      <c r="B11" s="46" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>Function Under Test</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>TestData</t>
         </is>
       </c>
-      <c r="D11" s="46" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="E11" s="46" t="inlineStr">
+      <c r="E11" s="31" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F11" s="46" t="inlineStr">
+      <c r="F11" s="31" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G11" s="46" t="inlineStr">
+      <c r="G11" s="31" t="inlineStr">
         <is>
           <t>DefectID</t>
         </is>
       </c>
     </row>
     <row r="12" ht="63" customHeight="1">
-      <c r="A12" s="46" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>TC01</t>
         </is>
       </c>
-      <c r="B12" s="46" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>performAction</t>
         </is>
       </c>
-      <c r="C12" s="47" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>performAction(1L, 100L, 10L, PRODUCE_FOOD, null, null) for an eliminated player</t>
         </is>
       </c>
-      <c r="D12" s="47" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'Eliminated players cannot take actions'</t>
         </is>
       </c>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-    </row>
-    <row r="13" ht="63" customHeight="1">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'Eliminated players cannot take actions'</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G12" s="31" t="n"/>
+    </row>
+    <row r="13" ht="72" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>TC02</t>
         </is>
       </c>
-      <c r="B13" s="46" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>performAction</t>
         </is>
       </c>
-      <c r="C13" s="47" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>performAction(1L, 100L, 10L, PRODUCE_FOOD, null, null), alive player owning City10, factory returns a mock command</t>
         </is>
       </c>
-      <c r="D13" s="47" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>result not null; command.execute() called; turnActionRepository.save called with foodBefore/foodAfter/soldiersBefore/soldiersAfter filled</t>
         </is>
       </c>
-      <c r="E13" s="46" t="n"/>
-      <c r="F13" s="46" t="n"/>
-      <c r="G13" s="46" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="46" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>TurnAction returned, command.execute() called once and saved with foodBefore 50, foodAfter 70, soldiersBefore 20, soldiersAfter 20</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>TC03</t>
         </is>
       </c>
-      <c r="B14" s="46" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>performAction</t>
         </is>
       </c>
-      <c r="C14" s="47" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>requestedAction = null</t>
         </is>
       </c>
-      <c r="D14" s="47" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'Action type is required'</t>
         </is>
       </c>
-      <c r="E14" s="46" t="n"/>
-      <c r="F14" s="46" t="n"/>
-      <c r="G14" s="46" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="46" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'Action type is required'</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G14" s="31" t="n"/>
+    </row>
+    <row r="15" ht="72" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>TC04</t>
         </is>
       </c>
-      <c r="B15" s="46" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>performAction</t>
         </is>
       </c>
-      <c r="C15" s="47" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>an action already exists for (game, turn, city) - submit the same action again</t>
         </is>
       </c>
-      <c r="D15" s="47" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>returns the existing TurnAction; commandFactory.createCommand and command.execute NOT called again</t>
         </is>
       </c>
-      <c r="E15" s="46" t="n"/>
-      <c r="F15" s="46" t="n"/>
-      <c r="G15" s="46" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="46" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>the existing TurnAction is returned unchanged; commandFactory.createCommand and turnActionRepository.save never called again</t>
+        </is>
+      </c>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G15" s="31" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>TC05</t>
         </is>
       </c>
-      <c r="B16" s="46" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>performAction</t>
         </is>
       </c>
-      <c r="C16" s="47" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>city is owned by another player</t>
         </is>
       </c>
-      <c r="D16" s="47" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'You do not own this city'</t>
         </is>
       </c>
-      <c r="E16" s="46" t="n"/>
-      <c r="F16" s="46" t="n"/>
-      <c r="G16" s="46" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="46" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'You do not own this city'</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G16" s="31" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>TC06</t>
         </is>
       </c>
-      <c r="B17" s="46" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>performAction</t>
         </is>
       </c>
-      <c r="C17" s="47" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>player belongs to a different game than gameId</t>
         </is>
       </c>
-      <c r="D17" s="47" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'Player does not belong to this game'</t>
         </is>
       </c>
-      <c r="E17" s="46" t="n"/>
-      <c r="F17" s="46" t="n"/>
-      <c r="G17" s="46" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="46" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'Player does not belong to this game'</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>TC07</t>
         </is>
       </c>
-      <c r="B18" s="46" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>performAction</t>
         </is>
       </c>
-      <c r="C18" s="47" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>gameRepository.findByIdForUpdate(99L) empty</t>
         </is>
       </c>
-      <c r="D18" s="47" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>throws ResourceNotFoundException 'Game not found with id: 99'</t>
         </is>
       </c>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="46" t="n"/>
-      <c r="G18" s="46" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="46" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>ResourceNotFoundException 'Game not found with id: 99'</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>TC08</t>
         </is>
       </c>
-      <c r="B19" s="46" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>performAction</t>
         </is>
       </c>
-      <c r="C19" s="47" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>cityRepository.findById(99L) empty</t>
         </is>
       </c>
-      <c r="D19" s="47" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>throws ResourceNotFoundException 'City not found: 99'</t>
         </is>
       </c>
-      <c r="E19" s="46" t="n"/>
-      <c r="F19" s="46" t="n"/>
-      <c r="G19" s="46" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="46" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>ResourceNotFoundException 'City not found: 99'</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="72" customHeight="1">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>TC09</t>
         </is>
       </c>
-      <c r="B20" s="46" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>performAction</t>
         </is>
       </c>
-      <c r="C20" s="47" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>requestedAction = SEND_ARMY</t>
         </is>
       </c>
-      <c r="D20" s="47" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>a SendArmyCommand is created (factory case SEND_ARMY) and the recorded TurnAction carries the returned army</t>
         </is>
       </c>
-      <c r="E20" s="46" t="n"/>
-      <c r="F20" s="46" t="n"/>
-      <c r="G20" s="46" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="46" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>a SendArmyCommand is created; the recorded TurnAction has actionType SEND_ARMY and carries the army returned by armyService.sendArmy</t>
+        </is>
+      </c>
+      <c r="F20" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>TC10</t>
         </is>
       </c>
-      <c r="B21" s="46" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>performAction</t>
         </is>
       </c>
-      <c r="C21" s="47" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>requestedAction = NONE</t>
         </is>
       </c>
-      <c r="D21" s="47" t="inlineStr">
+      <c r="D21" s="33" t="inlineStr">
         <is>
           <t>NoneCommand is created; TurnAction recorded with actionType NONE and army == null</t>
         </is>
       </c>
-      <c r="E21" s="46" t="n"/>
-      <c r="F21" s="46" t="n"/>
-      <c r="G21" s="46" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="46" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>a NoneCommand is created; TurnAction recorded with actionType NONE and army == null; armyService.sendArmy never called</t>
+        </is>
+      </c>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="72" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>TC11</t>
         </is>
       </c>
-      <c r="B22" s="46" t="inlineStr">
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>performAction</t>
         </is>
       </c>
-      <c r="C22" s="47" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>game status is WAITING / PLACEMENT / FINISHED</t>
         </is>
       </c>
-      <c r="D22" s="47" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>state machine validateActionSubmission rejects the action</t>
         </is>
       </c>
-      <c r="E22" s="46" t="n"/>
-      <c r="F22" s="46" t="n"/>
-      <c r="G22" s="46" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="46" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>the state machine rejects it with BusinessLogicException 'ไม่สามารถทำแอคชันได้ เกมกำลังรอผู้เล่นอื่น'</t>
+        </is>
+      </c>
+      <c r="F22" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>TC12</t>
         </is>
       </c>
-      <c r="B23" s="46" t="inlineStr">
+      <c r="B23" s="31" t="inlineStr">
         <is>
           <t>findTurnActions</t>
         </is>
       </c>
-      <c r="C23" s="47" t="inlineStr">
+      <c r="C23" s="33" t="inlineStr">
         <is>
           <t>turnActionRepository has 2 actions for (game1, turn3)</t>
         </is>
       </c>
-      <c r="D23" s="47" t="inlineStr">
+      <c r="D23" s="33" t="inlineStr">
         <is>
           <t>findTurnActions(1L, 3) returns those 2 actions</t>
         </is>
       </c>
-      <c r="E23" s="46" t="n"/>
-      <c r="F23" s="46" t="n"/>
-      <c r="G23" s="46" t="n"/>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>findTurnActions(1L, 3) returns the 2 stored actions</t>
+        </is>
+      </c>
+      <c r="F23" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G23" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2779,381 +3172,460 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="4"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Project Name</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="33" t="n"/>
-      <c r="D3" s="33" t="n"/>
-      <c r="E3" s="33" t="n"/>
-      <c r="F3" s="33" t="n"/>
-      <c r="G3" s="34" t="n"/>
+      <c r="C3" s="32" t="n"/>
+      <c r="D3" s="32" t="n"/>
+      <c r="E3" s="32" t="n"/>
+      <c r="F3" s="32" t="n"/>
+      <c r="G3" s="24" t="n"/>
     </row>
     <row r="4" ht="84" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>SystemUnderTest/Class under Test</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>TurnService</t>
         </is>
       </c>
-      <c r="C4" s="33" t="n"/>
-      <c r="D4" s="33" t="n"/>
-      <c r="E4" s="33" t="n"/>
-      <c r="F4" s="33" t="n"/>
-      <c r="G4" s="34" t="n"/>
+      <c r="C4" s="32" t="n"/>
+      <c r="D4" s="32" t="n"/>
+      <c r="E4" s="32" t="n"/>
+      <c r="F4" s="32" t="n"/>
+      <c r="G4" s="24" t="n"/>
     </row>
     <row r="5" ht="35.4" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
-        <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
-        </is>
-      </c>
-      <c r="C5" s="33" t="n"/>
-      <c r="D5" s="33" t="n"/>
-      <c r="E5" s="33" t="n"/>
-      <c r="F5" s="33" t="n"/>
-      <c r="G5" s="34" t="n"/>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6" ht="21" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
+      <c r="B6" s="34" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="33" t="n"/>
-      <c r="D6" s="33" t="n"/>
-      <c r="E6" s="33" t="n"/>
-      <c r="F6" s="33" t="n"/>
-      <c r="G6" s="34" t="n"/>
+      <c r="C6" s="32" t="n"/>
+      <c r="D6" s="32" t="n"/>
+      <c r="E6" s="32" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="24" t="n"/>
     </row>
     <row r="7" ht="35.4" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Mock TurnActionRepository, GameRepository, PlayerService, CityRepository, CommandFactory</t>
         </is>
       </c>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="33" t="n"/>
-      <c r="E7" s="33" t="n"/>
-      <c r="F7" s="33" t="n"/>
-      <c r="G7" s="34" t="n"/>
+      <c r="C7" s="32" t="n"/>
+      <c r="D7" s="32" t="n"/>
+      <c r="E7" s="32" t="n"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="24" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="46" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>TestCaseID</t>
         </is>
       </c>
-      <c r="B11" s="46" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>Function Under Test</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>TestData</t>
         </is>
       </c>
-      <c r="D11" s="46" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="E11" s="46" t="inlineStr">
+      <c r="E11" s="31" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F11" s="46" t="inlineStr">
+      <c r="F11" s="31" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G11" s="46" t="inlineStr">
+      <c r="G11" s="31" t="inlineStr">
         <is>
           <t>DefectID</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="46" t="inlineStr">
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>TC01</t>
         </is>
       </c>
-      <c r="B12" s="46" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>resolveAndAdvance</t>
         </is>
       </c>
-      <c r="C12" s="47" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>resolveAndAdvance(1L); game turn 1 IN_PROGRESS, cities [C1, C2] both actionUsedThisTurn = true, 2 alive players</t>
         </is>
       </c>
-      <c r="D12" s="47" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>processTurn and resolveBattles called; every city reset to actionUsedThisTurn = false; cityRepository.saveAll called; currentTurnNumber = 2; gameRepository.save called</t>
         </is>
       </c>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-    </row>
-    <row r="13" ht="21" customHeight="1">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>processTurn(1L, 1) and resolveBattles(1L, 1) called, both cities reset to actionUsedThisTurn false, cityRepository.saveAll called, currentTurnNumber 1 -&gt; 2 and game saved</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G12" s="31" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>TC02</t>
         </is>
       </c>
-      <c r="B13" s="46" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>resolveAndAdvance</t>
         </is>
       </c>
-      <c r="C13" s="47" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>cities [C1, C2, C3, C4] all acted</t>
         </is>
       </c>
-      <c r="D13" s="47" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>actionUsedThisTurn == false for ALL FOUR cities (none skipped)</t>
         </is>
       </c>
-      <c r="E13" s="46" t="n"/>
-      <c r="F13" s="46" t="n"/>
-      <c r="G13" s="46" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="46" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>all 4 acted cities end with actionUsedThisTurn false (none skipped)</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="n"/>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>TC03</t>
         </is>
       </c>
-      <c r="B14" s="46" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>resolveAndAdvance</t>
         </is>
       </c>
-      <c r="C14" s="47" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>only C1 has acted, C2 has not</t>
         </is>
       </c>
-      <c r="D14" s="47" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>returns the same game; processTurn/resolveBattles NOT called; turn number unchanged</t>
         </is>
       </c>
-      <c r="E14" s="46" t="n"/>
-      <c r="F14" s="46" t="n"/>
-      <c r="G14" s="46" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="46" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>returns the same game without resolving: processTurn and resolveBattles never called, turn stays 1</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G14" s="31" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>TC04</t>
         </is>
       </c>
-      <c r="B15" s="46" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>resolveAndAdvance</t>
         </is>
       </c>
-      <c r="C15" s="47" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>no alive player in the game</t>
         </is>
       </c>
-      <c r="D15" s="47" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'Game has no active players'</t>
         </is>
       </c>
-      <c r="E15" s="46" t="n"/>
-      <c r="F15" s="46" t="n"/>
-      <c r="G15" s="46" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="46" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'Game has no active players'</t>
+        </is>
+      </c>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G15" s="31" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>TC05</t>
         </is>
       </c>
-      <c r="B16" s="46" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>resolveAndAdvance</t>
         </is>
       </c>
-      <c r="C16" s="47" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>gameRepository.findByIdForUpdate(99L) empty</t>
         </is>
       </c>
-      <c r="D16" s="47" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>throws ResourceNotFoundException 'Game not found with id: 99'</t>
         </is>
       </c>
-      <c r="E16" s="46" t="n"/>
-      <c r="F16" s="46" t="n"/>
-      <c r="G16" s="46" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="46" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>ResourceNotFoundException 'Game not found with id: 99'</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G16" s="31" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>TC06</t>
         </is>
       </c>
-      <c r="B17" s="46" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>resolveAndAdvance</t>
         </is>
       </c>
-      <c r="C17" s="47" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>gameRepository.findById(gameId) after resolution returns a FINISHED game</t>
         </is>
       </c>
-      <c r="D17" s="47" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>returns that game immediately; no upkeep, no city reset, no save</t>
         </is>
       </c>
-      <c r="E17" s="46" t="n"/>
-      <c r="F17" s="46" t="n"/>
-      <c r="G17" s="46" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="46" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>the FINISHED game is returned directly: no upkeep, no saveAll, no game save</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>TC07</t>
         </is>
       </c>
-      <c r="B18" s="46" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>resolveAndAdvance</t>
         </is>
       </c>
-      <c r="C18" s="47" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>currentTurnNumber = 4 (isSeasonEnd true)</t>
         </is>
       </c>
-      <c r="D18" s="47" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>cityService.applySeasonUpkeep(gameId) called once</t>
         </is>
       </c>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="46" t="n"/>
-      <c r="G18" s="46" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="46" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>cityService.applySeasonUpkeep(1L) called once on turn 4 (season end)</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>TC08</t>
         </is>
       </c>
-      <c r="B19" s="46" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>resolveAndAdvance</t>
         </is>
       </c>
-      <c r="C19" s="47" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>currentTurnNumber = 3</t>
         </is>
       </c>
-      <c r="D19" s="47" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>applySeasonUpkeep NOT called</t>
         </is>
       </c>
-      <c r="E19" s="46" t="n"/>
-      <c r="F19" s="46" t="n"/>
-      <c r="G19" s="46" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="46" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>applySeasonUpkeep never called on turn 3</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="72" customHeight="1">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>TC09</t>
         </is>
       </c>
-      <c r="B20" s="46" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>resolveAndAdvance</t>
         </is>
       </c>
-      <c r="C20" s="47" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>game status not eligible for turn resolution (e.g. WAITING)</t>
         </is>
       </c>
-      <c r="D20" s="47" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>state machine validateTurnResolution throws</t>
         </is>
       </c>
-      <c r="E20" s="46" t="n"/>
-      <c r="F20" s="46" t="n"/>
-      <c r="G20" s="46" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="46" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>validateTurnResolution rejects it with BusinessLogicException 'ไม่สามารถจบเทิร์นได้ เกมกำลังรอผู้เล่นอื่น'</t>
+        </is>
+      </c>
+      <c r="F20" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>TC10</t>
         </is>
       </c>
-      <c r="B21" s="46" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>getCurrentGame</t>
         </is>
       </c>
-      <c r="C21" s="47" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>getCurrentGame(1L) with Game(id1)</t>
         </is>
       </c>
-      <c r="D21" s="47" t="inlineStr">
+      <c r="D21" s="33" t="inlineStr">
         <is>
           <t>returns that game</t>
         </is>
       </c>
-      <c r="E21" s="46" t="n"/>
-      <c r="F21" s="46" t="n"/>
-      <c r="G21" s="46" t="n"/>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>getCurrentGame(1L) returns the same Game instance the repository holds</t>
+        </is>
+      </c>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G21" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3173,16 +3645,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="4.33203125" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
     <col width="9.88671875" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
-    <col width="12" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
-    <col width="12.77734375" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
-    <col width="8.21875" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
-    <col width="13.21875" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
-    <col width="34.44140625" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
+    <col width="30" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="52" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+    <col width="60" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
+    <col width="13" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
+    <col width="14" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3222,60 +3694,203 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="90" customHeight="1">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-    </row>
-    <row r="3">
+      <c r="B2" s="18" t="inlineStr">
+        <is>
+          <t>DEF-SVC-01</t>
+        </is>
+      </c>
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>Survival roll cannot be forced from a test</t>
+        </is>
+      </c>
+      <c r="D2" s="19" t="inlineStr">
+        <is>
+          <t>BattleService TC07 assumes executeSurvival() can be made to return true, but KongmingCombatStrategy rolls ThreadLocalRandom (50%) inside the strategy and the project pins Mockito's subclass mock-maker, so the random branch has no seam.</t>
+        </is>
+      </c>
+      <c r="E2" s="19" t="inlineStr">
+        <is>
+          <t>KongmingCombatStrategy.java:8. Workaround in the test: replay the same siege up to 60 times and assert the branch effects when it fires (city kept at 1 soldier, army 0 and DESTROYED, one REBELLION GameEvent). A proper fix is an injectable Random.</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="n">
+        <v>46305</v>
+      </c>
+      <c r="G2" s="19" t="inlineStr">
+        <is>
+          <t>Opened</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-    </row>
-    <row r="4">
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>DEF-SVC-02</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>Network food cost is shared, not charged to the source city</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>CityService TC13 expects the whole 10 food to come off the source city (5/100/100); deductFoodFromNetwork splits the cost over every city of the connected network and adds the remainder to the triggering city.</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>3-city network, each food 100, cost 10 -&gt; perCityCost 3, remainder 1 on City1. Observed 96/97/97. TC12 (2-city network, 95/95) already follows the shared model, so TC13 is the row that disagrees.</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="n">
+        <v>46305</v>
+      </c>
+      <c r="G3" s="19" t="inlineStr">
+        <is>
+          <t>Opened</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="72" customHeight="1">
       <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-    </row>
-    <row r="5">
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>DEF-SVC-03</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>Season upkeep model in TC14 contradicts TC15</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>CityService TC14 expects the network drained to the soldier total (City1 0, City3 25). applySeasonUpkeep instead deducts sum(soldiers) spread evenly and only redistributes when a city's balance goes negative.</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>City1 food 100 soldiers 25 + City3 food 100 soldiers 25 -&gt; upkeep 50, share 25 each -&gt; 75/75, no starvation. TC15 uses the same code model (12/63) and passes, which shows TC14 is the wrong row.</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="n">
+        <v>46305</v>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>Opened</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="72" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-    </row>
-    <row r="6">
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>DEF-SVC-04</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>Deficit cities get no share when the network has no excess</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>CityService TC23 expects shares of 5 and 5 and both deficit cities at 10 soldiers. A city only adds to totalExcess when food &gt;= soldiers, so the fixture contributes 0 excess and share becomes 0.</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>C1(10/10) C2(5/15) C3(0/15): totalFood 15 &lt; totalSoldiers 40, totalExcess 0. Observed C1 keeps 10, C2 15 -&gt; 5, C3 15 -&gt; 0, 2 STARVATION events (CityService.java:241-263).</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="n">
+        <v>46305</v>
+      </c>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>Opened</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="72" customHeight="1">
       <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>DEF-SVC-05</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>Draft can offer fewer than three candidates</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>MarshalDraftService TC07 expects 3 offered candidates. prepareNextPlayer offers min(3, remaining pool) and does not refill, top up or report the shortfall.</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>4 marshals in the repository, ids 1 and 2 already held -&gt; only 2 MarshalCandidate rows saved (slots 1-2). Exclusion of held marshals is correct; the count is not.</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>46305</v>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>Opened</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="72" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>DEF-SVC-06</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>Placement starts the game with an empty roster</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>PlacementService TC10 expects the game to stay in PLACEMENT when no player is listed. With an empty list hasConflict is false, so the else branch runs and flips the game anyway.</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>Observed game.status IN_PROGRESS and currentTurnNumber 1 while playerRepository.saveAll([]) runs and no city gets an owner (PlacementService.java:51-70). A roster guard is missing.</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>46305</v>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>Opened</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3295,7 +3910,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="46" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
@@ -3306,16 +3921,16 @@
           <t>Project Name</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="26" t="n"/>
+      <c r="C3" s="26" t="n"/>
+      <c r="D3" s="26" t="n"/>
+      <c r="E3" s="26" t="n"/>
+      <c r="F3" s="26" t="n"/>
+      <c r="G3" s="27" t="n"/>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
@@ -3323,16 +3938,16 @@
           <t>SystemUnderTest/Class under Test</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>ArmyService</t>
         </is>
       </c>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="26" t="n"/>
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="26" t="n"/>
+      <c r="E4" s="26" t="n"/>
+      <c r="F4" s="26" t="n"/>
+      <c r="G4" s="27" t="n"/>
     </row>
     <row r="5" ht="21" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -3340,16 +3955,16 @@
           <t>Environment</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
-        </is>
-      </c>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="26" t="n"/>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="27" t="n"/>
     </row>
     <row r="6" ht="21" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -3357,31 +3972,31 @@
           <t>Date</t>
         </is>
       </c>
-      <c r="B6" s="45" t="n">
+      <c r="B6" s="30" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="25" t="n"/>
-      <c r="D6" s="25" t="n"/>
-      <c r="E6" s="25" t="n"/>
-      <c r="F6" s="25" t="n"/>
-      <c r="G6" s="26" t="n"/>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="26" t="n"/>
+      <c r="E6" s="26" t="n"/>
+      <c r="F6" s="26" t="n"/>
+      <c r="G6" s="27" t="n"/>
     </row>
     <row r="7" ht="45.6" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Mock ArmyRepository = [], Mock PlayerRepository = [Player(ID1), Player(ID2)], Mock CityRepository = [City(ID1, Player1), City(ID2,Player2)]</t>
         </is>
       </c>
-      <c r="C7" s="25" t="n"/>
-      <c r="D7" s="25" t="n"/>
-      <c r="E7" s="25" t="n"/>
-      <c r="F7" s="25" t="n"/>
-      <c r="G7" s="26" t="n"/>
+      <c r="C7" s="26" t="n"/>
+      <c r="D7" s="26" t="n"/>
+      <c r="E7" s="26" t="n"/>
+      <c r="F7" s="26" t="n"/>
+      <c r="G7" s="27" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="6" t="n"/>
@@ -3393,791 +4008,1031 @@
       <c r="G10" s="7" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="46" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>TestCaseID</t>
         </is>
       </c>
-      <c r="B11" s="46" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>Function Under Test</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>TestData</t>
         </is>
       </c>
-      <c r="D11" s="46" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="E11" s="46" t="inlineStr">
+      <c r="E11" s="31" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F11" s="46" t="inlineStr">
+      <c r="F11" s="31" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G11" s="46" t="inlineStr">
+      <c r="G11" s="31" t="inlineStr">
         <is>
           <t>DefectID</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="24.6" customHeight="1">
-      <c r="A12" s="46" t="inlineStr">
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>TC01</t>
         </is>
       </c>
-      <c r="B12" s="46" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>sendArmy</t>
         </is>
       </c>
-      <c r="C12" s="47" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>sendArmy(1L, 2L, 10, 3)</t>
         </is>
       </c>
-      <c r="D12" s="47" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>armyRepository.save called once -&gt; ArmyRepository.size() == 1</t>
         </is>
       </c>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-    </row>
-    <row r="13" ht="24.6" customHeight="1">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>armyRepository.save called once; 1 army stored (owner Player1, source City1, target City2, status TRAVELING)</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G12" s="31" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>TC02</t>
         </is>
       </c>
-      <c r="B13" s="46" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>sendArmy</t>
         </is>
       </c>
-      <c r="C13" s="47" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>1L, 2L, 10, 3 -&gt; sendArmy(1L, 3L, 10, 3)</t>
         </is>
       </c>
-      <c r="D13" s="47" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>City not found with id: 3 (ResourceNotFoundException)</t>
         </is>
       </c>
-      <c r="E13" s="46" t="n"/>
-      <c r="F13" s="46" t="n"/>
-      <c r="G13" s="46" t="n"/>
-    </row>
-    <row r="14" ht="24.6" customHeight="1">
-      <c r="A14" s="46" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>ResourceNotFoundException 'City not found with id: 3'; 0 armies stored</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="n"/>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>TC03</t>
         </is>
       </c>
-      <c r="B14" s="46" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>sendArmy</t>
         </is>
       </c>
-      <c r="C14" s="47" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>3L, 1L, 10, 3</t>
         </is>
       </c>
-      <c r="D14" s="47" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>City not found with id: 3 (ResourceNotFoundException)</t>
         </is>
       </c>
-      <c r="E14" s="46" t="n"/>
-      <c r="F14" s="46" t="n"/>
-      <c r="G14" s="46" t="n"/>
-    </row>
-    <row r="15" ht="24.6" customHeight="1">
-      <c r="A15" s="46" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>ResourceNotFoundException 'City not found with id: 3' before any army is built; 0 armies stored</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G14" s="31" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>TC04</t>
         </is>
       </c>
-      <c r="B15" s="46" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>sendArmy</t>
         </is>
       </c>
-      <c r="C15" s="47" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>1L, 2L, 0, 3</t>
         </is>
       </c>
-      <c r="D15" s="47" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>Army must contain at least one soldier</t>
         </is>
       </c>
-      <c r="E15" s="46" t="n"/>
-      <c r="F15" s="46" t="n"/>
-      <c r="G15" s="46" t="n"/>
-    </row>
-    <row r="16" ht="24.6" customHeight="1">
-      <c r="A16" s="46" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'Army must contain at least one soldier'; 0 armies stored</t>
+        </is>
+      </c>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G15" s="31" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>TC05</t>
         </is>
       </c>
-      <c r="B16" s="46" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>sendArmy</t>
         </is>
       </c>
-      <c r="C16" s="47" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>1L, 2L, -10, 3</t>
         </is>
       </c>
-      <c r="D16" s="47" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>Army must contain at least one soldier</t>
         </is>
       </c>
-      <c r="E16" s="46" t="n"/>
-      <c r="F16" s="46" t="n"/>
-      <c r="G16" s="46" t="n"/>
-    </row>
-    <row r="17" ht="49.2" customHeight="1">
-      <c r="A17" s="46" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'Army must contain at least one soldier'; 0 armies stored</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G16" s="31" t="n"/>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>TC06</t>
         </is>
       </c>
-      <c r="B17" s="46" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>sendArmy</t>
         </is>
       </c>
-      <c r="C17" s="47" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>1L, 2L, 51, 3; City1.soldiers = 50</t>
         </is>
       </c>
-      <c r="D17" s="47" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>Not enough soldiers in the city</t>
         </is>
       </c>
-      <c r="E17" s="46" t="n"/>
-      <c r="F17" s="46" t="n"/>
-      <c r="G17" s="46" t="n"/>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'Not enough soldiers in the city' (51 asked, City1 holds 50)</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G17" s="31" t="n"/>
     </row>
     <row r="18" ht="49.2" customHeight="1">
-      <c r="A18" s="46" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>TC07</t>
         </is>
       </c>
-      <c r="B18" s="46" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>sendArmy</t>
         </is>
       </c>
-      <c r="C18" s="47" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>1L, 2L, 50, 3; City1.soldiers = 50 (boundary)</t>
         </is>
       </c>
-      <c r="D18" s="47" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>ArmyRepository.size() == 1</t>
         </is>
       </c>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="46" t="n"/>
-      <c r="G18" s="46" t="n"/>
-    </row>
-    <row r="19" ht="24.6" customHeight="1">
-      <c r="A19" s="46" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>boundary accepted: 1 army stored and City1.soldiers 50 -&gt; 0</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>TC08</t>
         </is>
       </c>
-      <c r="B19" s="46" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>sendArmy</t>
         </is>
       </c>
-      <c r="C19" s="47" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>game.status = FINISHED</t>
         </is>
       </c>
-      <c r="D19" s="47" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>Game is not in progress</t>
         </is>
       </c>
-      <c r="E19" s="46" t="n"/>
-      <c r="F19" s="46" t="n"/>
-      <c r="G19" s="46" t="n"/>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'Game is not in progress'</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G19" s="31" t="n"/>
     </row>
     <row r="20" ht="49.2" customHeight="1">
-      <c r="A20" s="46" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>TC09</t>
         </is>
       </c>
-      <c r="B20" s="46" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>sendArmy</t>
         </is>
       </c>
-      <c r="C20" s="47" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>1L, 3L, 10, 3; City(3L).game = Game2</t>
         </is>
       </c>
-      <c r="D20" s="47" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>Target must be in the same game</t>
         </is>
       </c>
-      <c r="E20" s="46" t="n"/>
-      <c r="F20" s="46" t="n"/>
-      <c r="G20" s="46" t="n"/>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'Target must be in the same game'</t>
+        </is>
+      </c>
+      <c r="F20" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G20" s="31" t="n"/>
     </row>
     <row r="21" ht="49.2" customHeight="1">
-      <c r="A21" s="46" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>TC10</t>
         </is>
       </c>
-      <c r="B21" s="46" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>sendArmy</t>
         </is>
       </c>
-      <c r="C21" s="47" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>no MapEdge connecting city1-city2</t>
         </is>
       </c>
-      <c r="D21" s="47" t="inlineStr">
+      <c r="D21" s="33" t="inlineStr">
         <is>
           <t>You can only send an army to a directly connected city</t>
         </is>
       </c>
-      <c r="E21" s="46" t="n"/>
-      <c r="F21" s="46" t="n"/>
-      <c r="G21" s="46" t="n"/>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'You can only send an army to a directly connected city'</t>
+        </is>
+      </c>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G21" s="31" t="n"/>
     </row>
     <row r="22" ht="49.2" customHeight="1">
-      <c r="A22" s="46" t="inlineStr">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>TC11</t>
         </is>
       </c>
-      <c r="B22" s="46" t="inlineStr">
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>sendArmy</t>
         </is>
       </c>
-      <c r="C22" s="47" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>player1.isAlive = false</t>
         </is>
       </c>
-      <c r="D22" s="47" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>Eliminated players cannot command armies</t>
         </is>
       </c>
-      <c r="E22" s="46" t="n"/>
-      <c r="F22" s="46" t="n"/>
-      <c r="G22" s="46" t="n"/>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'Eliminated players cannot command armies'</t>
+        </is>
+      </c>
+      <c r="F22" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G22" s="31" t="n"/>
     </row>
     <row r="23" ht="49.2" customHeight="1">
-      <c r="A23" s="46" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>TC12</t>
         </is>
       </c>
-      <c r="B23" s="46" t="inlineStr">
+      <c r="B23" s="31" t="inlineStr">
         <is>
           <t>sendArmy</t>
         </is>
       </c>
-      <c r="C23" s="47" t="inlineStr">
+      <c r="C23" s="33" t="inlineStr">
         <is>
           <t>turnNumber in RAINY season</t>
         </is>
       </c>
-      <c r="D23" s="47" t="inlineStr">
+      <c r="D23" s="33" t="inlineStr">
         <is>
           <t>arrivalTurn - departureTurn == 4 (base 3 + 1 rainy)</t>
         </is>
       </c>
-      <c r="E23" s="46" t="n"/>
-      <c r="F23" s="46" t="n"/>
-      <c r="G23" s="46" t="n"/>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>arrivalTurn - departureTurn == 4 (base 3 turns + 1 for the RAINY season)</t>
+        </is>
+      </c>
+      <c r="F23" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G23" s="31" t="n"/>
     </row>
     <row r="24" ht="73.8" customHeight="1">
-      <c r="A24" s="46" t="inlineStr">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>TC13</t>
         </is>
       </c>
-      <c r="B24" s="46" t="inlineStr">
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>sendArmy</t>
         </is>
       </c>
-      <c r="C24" s="47" t="inlineStr">
+      <c r="C24" s="33" t="inlineStr">
         <is>
           <t>owner's Marshal travelsFaster() = true, normal season</t>
         </is>
       </c>
-      <c r="D24" s="47" t="inlineStr">
+      <c r="D24" s="33" t="inlineStr">
         <is>
           <t>arrivalTurn - departureTurn == 2 (base 3 - 1)</t>
         </is>
       </c>
-      <c r="E24" s="46" t="n"/>
-      <c r="F24" s="46" t="n"/>
-      <c r="G24" s="46" t="n"/>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>arrivalTurn - departureTurn == 2 (FASTER_TRAVEL marshal: base 3 - 1)</t>
+        </is>
+      </c>
+      <c r="F24" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G24" s="31" t="n"/>
     </row>
     <row r="25" ht="24.6" customHeight="1">
-      <c r="A25" s="46" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>TC14</t>
         </is>
       </c>
-      <c r="B25" s="46" t="inlineStr">
+      <c r="B25" s="31" t="inlineStr">
         <is>
           <t>cancelIfDestroyed</t>
         </is>
       </c>
-      <c r="C25" s="47" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
         <is>
           <t>Army(soldiers 0, status = TRAVELING)</t>
         </is>
       </c>
-      <c r="D25" s="47" t="inlineStr">
+      <c r="D25" s="33" t="inlineStr">
         <is>
           <t>verify(armyRepository).save(army) called once</t>
         </is>
       </c>
-      <c r="E25" s="46" t="n"/>
-      <c r="F25" s="46" t="n"/>
-      <c r="G25" s="46" t="n"/>
-    </row>
-    <row r="26" ht="24.6" customHeight="1">
-      <c r="A26" s="46" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>armyRepository.save(army) called once</t>
+        </is>
+      </c>
+      <c r="F25" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t>TC15</t>
         </is>
       </c>
-      <c r="B26" s="46" t="inlineStr">
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>cancelIfDestroyed</t>
         </is>
       </c>
-      <c r="C26" s="47" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
         <is>
           <t>Army(soldiers 10, status = ARRIVED)</t>
         </is>
       </c>
-      <c r="D26" s="47" t="inlineStr">
+      <c r="D26" s="33" t="inlineStr">
         <is>
           <t>verify(armyRepository, never()).save(army)</t>
         </is>
       </c>
-      <c r="E26" s="46" t="n"/>
-      <c r="F26" s="46" t="n"/>
-      <c r="G26" s="46" t="n"/>
-    </row>
-    <row r="27" ht="24.6" customHeight="1">
-      <c r="A27" s="46" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>armyRepository.save never called (army status is ARRIVED)</t>
+        </is>
+      </c>
+      <c r="F26" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>TC16</t>
         </is>
       </c>
-      <c r="B27" s="46" t="inlineStr">
+      <c r="B27" s="31" t="inlineStr">
         <is>
           <t>cancelIfDestroyed</t>
         </is>
       </c>
-      <c r="C27" s="47" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>Army(soldiers 10, status = TRAVELING)</t>
         </is>
       </c>
-      <c r="D27" s="47" t="inlineStr">
+      <c r="D27" s="33" t="inlineStr">
         <is>
           <t>verify(armyRepository, never()).save(army)</t>
         </is>
       </c>
-      <c r="E27" s="46" t="n"/>
-      <c r="F27" s="46" t="n"/>
-      <c r="G27" s="46" t="n"/>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>armyRepository.save never called (army still has 10 soldiers)</t>
+        </is>
+      </c>
+      <c r="F27" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G27" s="31" t="n"/>
     </row>
     <row r="28" ht="123" customHeight="1">
-      <c r="A28" s="46" t="inlineStr">
+      <c r="A28" s="31" t="inlineStr">
         <is>
           <t>TC17</t>
         </is>
       </c>
-      <c r="B28" s="46" t="inlineStr">
+      <c r="B28" s="31" t="inlineStr">
         <is>
           <t>findDueArmies</t>
         </is>
       </c>
-      <c r="C28" s="47" t="inlineStr">
+      <c r="C28" s="33" t="inlineStr">
         <is>
           <t>Game(ID=1), findDueArmies(1, 3), armyRepository = [army(soldiers 10, TRAVELING, arrivalTurn 2), army(soldiers 20, TRAVELING, arrivalTurn 2)]</t>
         </is>
       </c>
-      <c r="D28" s="47" t="inlineStr">
+      <c r="D28" s="33" t="inlineStr">
         <is>
           <t>result.size() == 2</t>
         </is>
       </c>
-      <c r="E28" s="46" t="n"/>
-      <c r="F28" s="46" t="n"/>
-      <c r="G28" s="46" t="n"/>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>findDueArmies(1L, 3) returns 2 armies</t>
+        </is>
+      </c>
+      <c r="F28" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G28" s="31" t="n"/>
     </row>
     <row r="29" ht="98.40000000000001" customHeight="1">
-      <c r="A29" s="46" t="inlineStr">
+      <c r="A29" s="31" t="inlineStr">
         <is>
           <t>TC18</t>
         </is>
       </c>
-      <c r="B29" s="46" t="inlineStr">
+      <c r="B29" s="31" t="inlineStr">
         <is>
           <t>findDueArmies</t>
         </is>
       </c>
-      <c r="C29" s="47" t="inlineStr">
+      <c r="C29" s="33" t="inlineStr">
         <is>
           <t>Game(ID=1), findDueArmies(1, 2), armyRepository = [army(10, TRAVELING, 2), army(20, TRAVELING, 3)]</t>
         </is>
       </c>
-      <c r="D29" s="47" t="inlineStr">
+      <c r="D29" s="33" t="inlineStr">
         <is>
           <t>result.size() == 1 (arrivalTurn &lt;= 2)</t>
         </is>
       </c>
-      <c r="E29" s="46" t="n"/>
-      <c r="F29" s="46" t="n"/>
-      <c r="G29" s="46" t="n"/>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>findDueArmies(1L, 2) returns 1 army (id 91, arrivalTurn 2); the arrivalTurn 3 army is excluded</t>
+        </is>
+      </c>
+      <c r="F29" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G29" s="31" t="n"/>
     </row>
     <row r="30" ht="98.40000000000001" customHeight="1">
-      <c r="A30" s="46" t="inlineStr">
+      <c r="A30" s="31" t="inlineStr">
         <is>
           <t>TC19</t>
         </is>
       </c>
-      <c r="B30" s="46" t="inlineStr">
+      <c r="B30" s="31" t="inlineStr">
         <is>
           <t>findByOwner</t>
         </is>
       </c>
-      <c r="C30" s="47" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
         <is>
           <t>armyRepository = [army(owner Player(id1), 10, TRAVELING, 2), army(owner Player(id1), 20, TRAVELING, 3)], parameter = 1</t>
         </is>
       </c>
-      <c r="D30" s="47" t="inlineStr">
+      <c r="D30" s="33" t="inlineStr">
         <is>
           <t>result.size() == 2</t>
         </is>
       </c>
-      <c r="E30" s="46" t="n"/>
-      <c r="F30" s="46" t="n"/>
-      <c r="G30" s="46" t="n"/>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>findByOwner(1L) returns the 2 traveling armies of Player1</t>
+        </is>
+      </c>
+      <c r="F30" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G30" s="31" t="n"/>
     </row>
     <row r="31" ht="98.40000000000001" customHeight="1">
-      <c r="A31" s="46" t="inlineStr">
+      <c r="A31" s="31" t="inlineStr">
         <is>
           <t>TC20</t>
         </is>
       </c>
-      <c r="B31" s="46" t="inlineStr">
+      <c r="B31" s="31" t="inlineStr">
         <is>
           <t>findByOwner</t>
         </is>
       </c>
-      <c r="C31" s="47" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
         <is>
           <t>same armies as TC19, parameter = 2</t>
         </is>
       </c>
-      <c r="D31" s="47" t="inlineStr">
+      <c r="D31" s="33" t="inlineStr">
         <is>
           <t>result.size() == 0</t>
         </is>
       </c>
-      <c r="E31" s="46" t="n"/>
-      <c r="F31" s="46" t="n"/>
-      <c r="G31" s="46" t="n"/>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>findByOwner(2L) returns an empty list</t>
+        </is>
+      </c>
+      <c r="F31" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G31" s="31" t="n"/>
     </row>
     <row r="32" ht="49.2" customHeight="1">
-      <c r="A32" s="46" t="inlineStr">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t>TC21</t>
         </is>
       </c>
-      <c r="B32" s="46" t="inlineStr">
+      <c r="B32" s="31" t="inlineStr">
         <is>
           <t>findById</t>
         </is>
       </c>
-      <c r="C32" s="47" t="inlineStr">
+      <c r="C32" s="33" t="inlineStr">
         <is>
           <t>armyRepository = [army(id1), army(id2)], parameter = 1</t>
         </is>
       </c>
-      <c r="D32" s="47" t="inlineStr">
+      <c r="D32" s="33" t="inlineStr">
         <is>
           <t>army.getId() == 1</t>
         </is>
       </c>
-      <c r="E32" s="46" t="n"/>
-      <c r="F32" s="46" t="n"/>
-      <c r="G32" s="46" t="n"/>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>findById(1L).getId() == 1</t>
+        </is>
+      </c>
+      <c r="F32" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G32" s="31" t="n"/>
     </row>
     <row r="33" ht="49.2" customHeight="1">
-      <c r="A33" s="46" t="inlineStr">
+      <c r="A33" s="31" t="inlineStr">
         <is>
           <t>TC22</t>
         </is>
       </c>
-      <c r="B33" s="46" t="inlineStr">
+      <c r="B33" s="31" t="inlineStr">
         <is>
           <t>findById</t>
         </is>
       </c>
-      <c r="C33" s="47" t="inlineStr">
+      <c r="C33" s="33" t="inlineStr">
         <is>
           <t>armyRepository = [army(id1), army(id2)], parameter = 3</t>
         </is>
       </c>
-      <c r="D33" s="47" t="inlineStr">
+      <c r="D33" s="33" t="inlineStr">
         <is>
           <t>Army not found with id: 3</t>
         </is>
       </c>
-      <c r="E33" s="46" t="n"/>
-      <c r="F33" s="46" t="n"/>
-      <c r="G33" s="46" t="n"/>
-    </row>
-    <row r="34" ht="24.6" customHeight="1">
-      <c r="A34" s="46" t="inlineStr">
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>ResourceNotFoundException 'Army not found with id: 3'</t>
+        </is>
+      </c>
+      <c r="F33" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G33" s="31" t="n"/>
+    </row>
+    <row r="34" ht="54" customHeight="1">
+      <c r="A34" s="31" t="inlineStr">
         <is>
           <t>TC23</t>
         </is>
       </c>
-      <c r="B34" s="46" t="inlineStr">
+      <c r="B34" s="31" t="inlineStr">
         <is>
           <t>sendArmy</t>
         </is>
       </c>
-      <c r="C34" s="47" t="inlineStr">
+      <c r="C34" s="33" t="inlineStr">
         <is>
           <t>sendArmy(1L, 2L, 10, 3), owner's Marshal has no special multiplier (StandardMarshalStrategy = 1.0)</t>
         </is>
       </c>
-      <c r="D34" s="47" t="inlineStr">
+      <c r="D34" s="33" t="inlineStr">
         <is>
           <t>verify(cityService).deductFoodFromNetwork(sourceCity, 12)  [floor(10 * 1.25 * 1.0)]</t>
         </is>
       </c>
-      <c r="E34" s="46" t="n"/>
-      <c r="F34" s="46" t="n"/>
-      <c r="G34" s="46" t="n"/>
-    </row>
-    <row r="35" ht="24.6" customHeight="1">
-      <c r="A35" s="46" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>cityService.deductFoodFromNetwork(City1, 12) called once = floor(10 * 1.25 * 1.0)</t>
+        </is>
+      </c>
+      <c r="F34" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G34" s="31" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="31" t="inlineStr">
         <is>
           <t>TC24</t>
         </is>
       </c>
-      <c r="B35" s="46" t="inlineStr">
+      <c r="B35" s="31" t="inlineStr">
         <is>
           <t>sendArmy</t>
         </is>
       </c>
-      <c r="C35" s="47" t="inlineStr">
+      <c r="C35" s="33" t="inlineStr">
         <is>
           <t>sendArmy(1L, 2L, 10, 3) succeeds</t>
         </is>
       </c>
-      <c r="D35" s="47" t="inlineStr">
+      <c r="D35" s="33" t="inlineStr">
         <is>
           <t>sourceCity.getSoldiers() reduced by exactly 10</t>
         </is>
       </c>
-      <c r="E35" s="46" t="n"/>
-      <c r="F35" s="46" t="n"/>
-      <c r="G35" s="46" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="46" t="inlineStr">
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>City1.soldiers 50 -&gt; 40, exactly the 10 requested removed</t>
+        </is>
+      </c>
+      <c r="F35" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G35" s="31" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="31" t="inlineStr">
         <is>
           <t>TC25</t>
         </is>
       </c>
-      <c r="B36" s="46" t="inlineStr">
+      <c r="B36" s="31" t="inlineStr">
         <is>
           <t>sendArmy</t>
         </is>
       </c>
-      <c r="C36" s="47" t="inlineStr">
+      <c r="C36" s="33" t="inlineStr">
         <is>
           <t>sendArmy(1L, 2L, 10, 3) succeeds</t>
         </is>
       </c>
-      <c r="D36" s="47" t="inlineStr">
+      <c r="D36" s="33" t="inlineStr">
         <is>
           <t>sourceCity.getActionUsedThisTurn() == true</t>
         </is>
       </c>
-      <c r="E36" s="46" t="n"/>
-      <c r="F36" s="46" t="n"/>
-      <c r="G36" s="46" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="46" t="inlineStr">
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>City1.actionUsedThisTurn == true</t>
+        </is>
+      </c>
+      <c r="F36" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G36" s="31" t="n"/>
+    </row>
+    <row r="37" ht="54" customHeight="1">
+      <c r="A37" s="31" t="inlineStr">
         <is>
           <t>TC26</t>
         </is>
       </c>
-      <c r="B37" s="46" t="inlineStr">
+      <c r="B37" s="31" t="inlineStr">
         <is>
           <t>sendArmy</t>
         </is>
       </c>
-      <c r="C37" s="47" t="inlineStr">
+      <c r="C37" s="33" t="inlineStr">
         <is>
           <t>sendArmy(1L, 2L, 10, 3) succeeds</t>
         </is>
       </c>
-      <c r="D37" s="47" t="inlineStr">
+      <c r="D37" s="33" t="inlineStr">
         <is>
           <t>verify(cityRepository).save(sourceCity) and verify(armyRepository).save(any(Army.class)) each called once</t>
         </is>
       </c>
-      <c r="E37" s="46" t="n"/>
-      <c r="F37" s="46" t="n"/>
-      <c r="G37" s="46" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="46" t="inlineStr">
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>cityRepository.save(City1) once and armyRepository.save(any Army) once</t>
+        </is>
+      </c>
+      <c r="F37" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G37" s="31" t="n"/>
+    </row>
+    <row r="38" ht="54" customHeight="1">
+      <c r="A38" s="31" t="inlineStr">
         <is>
           <t>TC27</t>
         </is>
       </c>
-      <c r="B38" s="46" t="inlineStr">
+      <c r="B38" s="31" t="inlineStr">
         <is>
           <t>sendArmy</t>
         </is>
       </c>
-      <c r="C38" s="47" t="inlineStr">
+      <c r="C38" s="33" t="inlineStr">
         <is>
           <t>inspect the saved Army after sendArmy(1L, 2L, 10, 3)</t>
         </is>
       </c>
-      <c r="D38" s="47" t="inlineStr">
+      <c r="D38" s="33" t="inlineStr">
         <is>
           <t>army.getStatus() == TRAVELING, departureTurn == turnNumber, arrivalTurn == turnNumber + travelTurns</t>
         </is>
       </c>
-      <c r="E38" s="46" t="n"/>
-      <c r="F38" s="46" t="n"/>
-      <c r="G38" s="46" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="46" t="inlineStr">
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>stored army: status TRAVELING, departureTurn 3, arrivalTurn 6 (turnNumber + 3 travel turns)</t>
+        </is>
+      </c>
+      <c r="F38" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G38" s="31" t="n"/>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="31" t="inlineStr">
         <is>
           <t>TC28</t>
         </is>
       </c>
-      <c r="B39" s="46" t="inlineStr">
+      <c r="B39" s="31" t="inlineStr">
         <is>
           <t>cancelIfDestroyed</t>
         </is>
       </c>
-      <c r="C39" s="47" t="inlineStr">
+      <c r="C39" s="33" t="inlineStr">
         <is>
           <t>Army(soldiers 0, status = TRAVELING)</t>
         </is>
       </c>
-      <c r="D39" s="47" t="inlineStr">
+      <c r="D39" s="33" t="inlineStr">
         <is>
           <t>after the call army.getStatus() == CANCELLED and army.getSoldiers() == 0</t>
         </is>
       </c>
-      <c r="E39" s="46" t="n"/>
-      <c r="F39" s="46" t="n"/>
-      <c r="G39" s="46" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="46" t="inlineStr">
+      <c r="E39" s="21" t="inlineStr">
+        <is>
+          <t>after the call army.getStatus() == CANCELLED and army.getSoldiers() == 0</t>
+        </is>
+      </c>
+      <c r="F39" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G39" s="31" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="31" t="inlineStr">
         <is>
           <t>TC29</t>
         </is>
       </c>
-      <c r="B40" s="46" t="inlineStr">
+      <c r="B40" s="31" t="inlineStr">
         <is>
           <t>findDueArmies</t>
         </is>
       </c>
-      <c r="C40" s="47" t="inlineStr">
+      <c r="C40" s="33" t="inlineStr">
         <is>
           <t>findDueArmies(1, 5), armyRepository = []</t>
         </is>
       </c>
-      <c r="D40" s="47" t="inlineStr">
+      <c r="D40" s="33" t="inlineStr">
         <is>
           <t>result.isEmpty() == true, no exception</t>
         </is>
       </c>
-      <c r="E40" s="46" t="n"/>
-      <c r="F40" s="46" t="n"/>
-      <c r="G40" s="46" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="46" t="inlineStr">
+      <c r="E40" s="21" t="inlineStr">
+        <is>
+          <t>empty list returned, no exception raised</t>
+        </is>
+      </c>
+      <c r="F40" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G40" s="31" t="n"/>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="31" t="inlineStr">
         <is>
           <t>TC30</t>
         </is>
       </c>
-      <c r="B41" s="46" t="inlineStr">
+      <c r="B41" s="31" t="inlineStr">
         <is>
           <t>findById</t>
         </is>
       </c>
-      <c r="C41" s="47" t="inlineStr">
+      <c r="C41" s="33" t="inlineStr">
         <is>
           <t>armyRepository = [], findById(1)</t>
         </is>
       </c>
-      <c r="D41" s="47" t="inlineStr">
+      <c r="D41" s="33" t="inlineStr">
         <is>
           <t>Army not found with id: 1 (ResourceNotFoundException)</t>
         </is>
       </c>
-      <c r="E41" s="46" t="n"/>
-      <c r="F41" s="46" t="n"/>
-      <c r="G41" s="46" t="n"/>
+      <c r="E41" s="21" t="inlineStr">
+        <is>
+          <t>ResourceNotFoundException 'Army not found with id: 1'</t>
+        </is>
+      </c>
+      <c r="F41" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G41" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4201,383 +5056,474 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="22" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="59.77734375" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="4"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Project Name</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Eternal Crash2</t>
         </is>
       </c>
     </row>
     <row r="4" ht="84" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>SystemUnderTest/Class under Test</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>BattleService</t>
         </is>
       </c>
     </row>
     <row r="5" ht="35.4" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
         </is>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B6" s="39" t="n">
+      <c r="B6" s="12" t="n">
         <v>46305</v>
       </c>
     </row>
     <row r="7" ht="61.2" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mock ArmyRepository, BattleRepository, CityRepository, PlayerRepository, GameRepository = [Game(id 1L) , GameEventRepository, GameRuleService; </t>
         </is>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="46" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>TestCaseID</t>
         </is>
       </c>
-      <c r="B11" s="46" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>Function Under Test</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>TestData</t>
         </is>
       </c>
-      <c r="D11" s="46" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="E11" s="46" t="inlineStr">
+      <c r="E11" s="31" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F11" s="46" t="inlineStr">
+      <c r="F11" s="31" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G11" s="46" t="inlineStr">
+      <c r="G11" s="31" t="inlineStr">
         <is>
           <t>DefectID</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="63" customHeight="1">
-      <c r="A12" s="46" t="inlineStr">
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>TC01</t>
         </is>
       </c>
-      <c r="B12" s="46" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>resolveBattles</t>
         </is>
       </c>
-      <c r="C12" s="47" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>resolveBattles(1L, 1); attacker army 100 soldiers vs city(defender, 10 soldiers)</t>
         </is>
       </c>
-      <c r="D12" s="47" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>army == DESTROYED; city captured by attacker; checkPlayerElimination(defender,1) and checkWinCondition(game) called; battle saved</t>
         </is>
       </c>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>army DESTROYED, city owner becomes the attacker, checkPlayerElimination(defender, 1) and checkWinCondition(game) called, 1 battle saved (ATTACKER_WIN, isCityDestroyed true)</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G12" s="31" t="n"/>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>TC02</t>
         </is>
       </c>
-      <c r="B13" s="46" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>resolveBattles</t>
         </is>
       </c>
-      <c r="C13" s="47" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>resolveBattles(1L, 1); attacker army 10 soldiers vs city(defender, 100 soldiers)</t>
         </is>
       </c>
-      <c r="D13" s="47" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>army == DESTROYED; city NOT captured (still defender's); city.soldiers &gt; 0; battle saved</t>
         </is>
       </c>
-      <c r="E13" s="46" t="n"/>
-      <c r="F13" s="46" t="n"/>
-      <c r="G13" s="46" t="n"/>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>army DESTROYED, city still owned by the defender with 90 soldiers left, 1 battle saved (DEFENDER_WIN)</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="n"/>
     </row>
     <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="46" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>TC03</t>
         </is>
       </c>
-      <c r="B14" s="46" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>findById</t>
         </is>
       </c>
-      <c r="C14" s="47" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>findById(2L), battleRepository = [Battle(id1)]</t>
         </is>
       </c>
-      <c r="D14" s="47" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>Battle not found with id: 2 (ResourceNotFoundException)</t>
         </is>
       </c>
-      <c r="E14" s="46" t="n"/>
-      <c r="F14" s="46" t="n"/>
-      <c r="G14" s="46" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="46" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>ResourceNotFoundException 'Battle not found with id: 2'</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G14" s="31" t="n"/>
+    </row>
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>TC04</t>
         </is>
       </c>
-      <c r="B15" s="46" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>resolveBattles</t>
         </is>
       </c>
-      <c r="C15" s="47" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>army(10) arrives at a city already owned by the sending player</t>
         </is>
       </c>
-      <c r="D15" s="47" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>city.soldiers += 10; army.soldiers == 0 and status == DESTROYED; NO battle record saved</t>
         </is>
       </c>
-      <c r="E15" s="46" t="n"/>
-      <c r="F15" s="46" t="n"/>
-      <c r="G15" s="46" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="46" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>reinforcement branch: friendly city 10 -&gt; 20 soldiers, army soldiers 0 and status DESTROYED, no battle record saved</t>
+        </is>
+      </c>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G15" s="31" t="n"/>
+    </row>
+    <row r="16" ht="72" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>TC05</t>
         </is>
       </c>
-      <c r="B16" s="46" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>resolveBattles</t>
         </is>
       </c>
-      <c r="C16" s="47" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>two armies of different owners on the same edge in opposite directions, A(city1-&gt;city2) B(city2-&gt;city1), both departureTurn &lt; turn</t>
         </is>
       </c>
-      <c r="D16" s="47" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>field battle: soldiers reduced by kills, destroyed armies set CANCELLED, 1 FIELD_ENCOUNTER battle saved with isCityDestroyed == false</t>
         </is>
       </c>
-      <c r="E16" s="46" t="n"/>
-      <c r="F16" s="46" t="n"/>
-      <c r="G16" s="46" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="46" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>field encounter at turn 2: army 60 -&gt; 20 soldiers, enemy army 40 -&gt; 0 and set CANCELLED, 1 FIELD_ENCOUNTER battle saved with isCityDestroyed false</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G16" s="31" t="n"/>
+    </row>
+    <row r="17" ht="72" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>TC06</t>
         </is>
       </c>
-      <c r="B17" s="46" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>resolveBattles</t>
         </is>
       </c>
-      <c r="C17" s="47" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>attacker army 50 vs neutral city(soldiers 30, player == null)</t>
         </is>
       </c>
-      <c r="D17" s="47" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>neutral deals 1-to-1 damage; city captured, city.player = attacker, city.soldiers == 20, city.food == 0; checkPlayerElimination NOT called (no defender)</t>
         </is>
       </c>
-      <c r="E17" s="46" t="n"/>
-      <c r="F17" s="46" t="n"/>
-      <c r="G17" s="46" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="46" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>neutral city trades 1-for-1: city captured (player == attacker, soldiers 50 - 30 == 20, food 0), checkPlayerElimination never called</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="108" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>TC07</t>
         </is>
       </c>
-      <c r="B18" s="46" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>resolveBattles</t>
         </is>
       </c>
-      <c r="C18" s="47" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>defender's Marshal specialAbilityType = SURVIVE_DESTRUCTION and executeSurvival() returns true</t>
         </is>
       </c>
-      <c r="D18" s="47" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>city NOT captured, city.soldiers == 1; army.soldiers == 0 DESTROYED; REBELLION GameEvent saved</t>
         </is>
       </c>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="46" t="n"/>
-      <c r="G18" s="46" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="46" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>survival is a 50% random roll, so the same siege was replayed up to 60 times: on the roll that survived the city kept 1 soldier and stayed with the defender, army 0/DESTROYED and 1 REBELLION GameEvent saved</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G18" s="31" t="inlineStr">
+        <is>
+          <t>DEF-SVC-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="72" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>TC08</t>
         </is>
       </c>
-      <c r="B19" s="46" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>resolveBattles</t>
         </is>
       </c>
-      <c r="C19" s="47" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>attackers remaining &gt; 0 but defenders remaining &gt; 0 (failed siege)</t>
         </is>
       </c>
-      <c r="D19" s="47" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>army.soldiers == 0, status == DESTROYED (attackers wiped out); battle result == DEFENDER_WIN</t>
         </is>
       </c>
-      <c r="E19" s="46" t="n"/>
-      <c r="F19" s="46" t="n"/>
-      <c r="G19" s="46" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="46" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>failed siege wipes the attackers: army 40 -&gt; 0 soldiers and DESTROYED even though 10 defenders were left; battle result DEFENDER_WIN</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="108" customHeight="1">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>TC09</t>
         </is>
       </c>
-      <c r="B20" s="46" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>resolveBattles</t>
         </is>
       </c>
-      <c r="C20" s="47" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>two armies arrive at the same city in the same turn</t>
         </is>
       </c>
-      <c r="D20" s="47" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>both resolved sequentially; the second one sees the city owner left by the first; armies with soldiers &lt;= 0 are skipped</t>
         </is>
       </c>
-      <c r="E20" s="46" t="n"/>
-      <c r="F20" s="46" t="n"/>
-      <c r="G20" s="46" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="46" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>first army (30 vs 10) takes the city and leaves 20 soldiers, the second army (20) then reinforces that same city to 40 and is consumed, a third army with 0 soldiers is skipped and stays TRAVELING; 1 battle saved</t>
+        </is>
+      </c>
+      <c r="F20" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>TC10</t>
         </is>
       </c>
-      <c r="B21" s="46" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>resolveBattles</t>
         </is>
       </c>
-      <c r="C21" s="47" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>resolveBattles(1L, 1) with no TRAVELING army due this turn</t>
         </is>
       </c>
-      <c r="D21" s="47" t="inlineStr">
+      <c r="D21" s="33" t="inlineStr">
         <is>
           <t>no battleRepository.save, no army status change</t>
         </is>
       </c>
-      <c r="E21" s="46" t="n"/>
-      <c r="F21" s="46" t="n"/>
-      <c r="G21" s="46" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="46" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>nothing due this turn: army untouched at 50 soldiers and TRAVELING, no battle saved, checkWinCondition never called</t>
+        </is>
+      </c>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="72" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>TC11</t>
         </is>
       </c>
-      <c r="B22" s="46" t="inlineStr">
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>resolveBattles</t>
         </is>
       </c>
-      <c r="C22" s="47" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>battle causes game.status = FINISHED inside the loop</t>
         </is>
       </c>
-      <c r="D22" s="47" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>loop breaks immediately, remaining armies not resolved</t>
         </is>
       </c>
-      <c r="E22" s="46" t="n"/>
-      <c r="F22" s="46" t="n"/>
-      <c r="G22" s="46" t="n"/>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>loop breaks on FINISHED: first army resolves to 0 soldiers, the second army is never touched (30 soldiers, TRAVELING), only 1 battle saved</t>
+        </is>
+      </c>
+      <c r="F22" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G22" s="31" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4594,758 +5540,977 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="46" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="46" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="92" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="46" bestFit="1" customWidth="1" min="3" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Project Name</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Eternal Crash2</t>
         </is>
       </c>
     </row>
     <row r="4" ht="84" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>SystemUnderTest/Class under Test</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>CityService</t>
         </is>
       </c>
     </row>
     <row r="5" ht="35.4" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
         </is>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B6" s="39" t="n">
+      <c r="B6" s="12" t="n">
         <v>46305</v>
       </c>
     </row>
     <row r="7" ht="35.4" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Mock CityRepository, PlayerRepository, PlayerService, MapEdgeRepository; alive player(ID100) with new PlayerStats</t>
         </is>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="46" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>TestCaseID</t>
         </is>
       </c>
-      <c r="B11" s="46" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>Function Under Test</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>TestData</t>
         </is>
       </c>
-      <c r="D11" s="46" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="E11" s="46" t="inlineStr">
+      <c r="E11" s="31" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F11" s="46" t="inlineStr">
+      <c r="F11" s="31" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G11" s="46" t="inlineStr">
+      <c r="G11" s="31" t="inlineStr">
         <is>
           <t>DefectID</t>
         </is>
       </c>
     </row>
     <row r="12" ht="63" customHeight="1">
-      <c r="A12" s="46" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>TC01</t>
         </is>
       </c>
-      <c r="B12" s="46" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>produceFood</t>
         </is>
       </c>
-      <c r="C12" s="47" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>produceFood(10L, 1); City(ID10, food=100) owned by alive player, Player.marshal = Marshal(foodProduction 20)</t>
         </is>
       </c>
-      <c r="D12" s="47" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>food == 120; actionUsedThisTurn == true; stats.totalFoodProduced == 20</t>
         </is>
       </c>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>food 100 -&gt; 120, actionUsedThisTurn true, stats.totalFoodProduced == 20</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G12" s="31" t="n"/>
     </row>
     <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>TC02</t>
         </is>
       </c>
-      <c r="B13" s="46" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>produceFood</t>
         </is>
       </c>
-      <c r="C13" s="47" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>produceFood(1L, 1) but repository holds City(ID10, food=100)</t>
         </is>
       </c>
-      <c r="D13" s="47" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>City not found: 1 (ResourceNotFoundException)</t>
         </is>
       </c>
-      <c r="E13" s="46" t="n"/>
-      <c r="F13" s="46" t="n"/>
-      <c r="G13" s="46" t="n"/>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>ResourceNotFoundException 'City not found: 1'</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="n"/>
     </row>
     <row r="14" ht="63" customHeight="1">
-      <c r="A14" s="46" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>TC03</t>
         </is>
       </c>
-      <c r="B14" s="46" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>produceFood</t>
         </is>
       </c>
-      <c r="C14" s="47" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>produceFood(10L, 10); City(ID10, food=100), Player.marshal = Marshal(foodProduction 20) -&gt; turn 10 is WINTER</t>
         </is>
       </c>
-      <c r="D14" s="47" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>food == 110 (20/2 halved); actionUsedThisTurn == true; stats.totalFoodProduced == 10</t>
         </is>
       </c>
-      <c r="E14" s="46" t="n"/>
-      <c r="F14" s="46" t="n"/>
-      <c r="G14" s="46" t="n"/>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>WINTER halves the production: food 100 -&gt; 110, totalFoodProduced == 10</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G14" s="31" t="n"/>
     </row>
     <row r="15" ht="63" customHeight="1">
-      <c r="A15" s="46" t="inlineStr">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>TC04</t>
         </is>
       </c>
-      <c r="B15" s="46" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>recruitSoldiers</t>
         </is>
       </c>
-      <c r="C15" s="47" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>recruitSoldiers(10L, 1); City(ID10, food=100, soldiers=30), Marshal(soldierProduction 20), turn 1 = SUMMER -&gt; 20-5=15</t>
         </is>
       </c>
-      <c r="D15" s="47" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>soldiers == 45; food == 80 (100-20); actionUsedThisTurn == true; stats.totalSoldiersRecruited == 15</t>
         </is>
       </c>
-      <c r="E15" s="46" t="n"/>
-      <c r="F15" s="46" t="n"/>
-      <c r="G15" s="46" t="n"/>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>soldiers 30 -&gt; 45, food 100 -&gt; 80, totalSoldiersRecruited == 15 (SUMMER 20 - 5)</t>
+        </is>
+      </c>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G15" s="31" t="n"/>
     </row>
     <row r="16" ht="63" customHeight="1">
-      <c r="A16" s="46" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>TC05</t>
         </is>
       </c>
-      <c r="B16" s="46" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>recruitSoldiers</t>
         </is>
       </c>
-      <c r="C16" s="47" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>recruitSoldiers(10L, 1); City(ID10, food=10) network has too little food</t>
         </is>
       </c>
-      <c r="D16" s="47" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException (Not enough food in the connected network)</t>
         </is>
       </c>
-      <c r="E16" s="46" t="n"/>
-      <c r="F16" s="46" t="n"/>
-      <c r="G16" s="46" t="n"/>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException starting with 'Not enough food in the connected network'</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G16" s="31" t="n"/>
     </row>
     <row r="17" ht="63" customHeight="1">
-      <c r="A17" s="46" t="inlineStr">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>TC06</t>
         </is>
       </c>
-      <c r="B17" s="46" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>recruitSoldiers</t>
         </is>
       </c>
-      <c r="C17" s="47" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>recruitSoldiers(10L, 6); City(ID10, food=100, soldiers=40), Marshal(soldierProduction 20), turn 6 = RAINY</t>
         </is>
       </c>
-      <c r="D17" s="47" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>soldiers == 60; food == 80; actionUsedThisTurn == true; stats.totalSoldiersRecruited == 20</t>
         </is>
       </c>
-      <c r="E17" s="46" t="n"/>
-      <c r="F17" s="46" t="n"/>
-      <c r="G17" s="46" t="n"/>
-    </row>
-    <row r="18" ht="63" customHeight="1">
-      <c r="A18" s="46" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>RAINY keeps the full production: soldiers 40 -&gt; 60, food 100 -&gt; 80, totalSoldiersRecruited == 20</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="72" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>TC07</t>
         </is>
       </c>
-      <c r="B18" s="46" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>getConnectedNetwork</t>
         </is>
       </c>
-      <c r="C18" s="47" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>getConnectedNetwork(City(id1, Game1, Player1)); MapEdgeRepository = [mapEdge(id1, Game1, City(id2), City(id3))], City1 and City2 owned by Player1</t>
         </is>
       </c>
-      <c r="D18" s="47" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>network.size() == 2</t>
         </is>
       </c>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="46" t="n"/>
-      <c r="G18" s="46" t="n"/>
-    </row>
-    <row r="19" ht="63" customHeight="1">
-      <c r="A19" s="46" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>network size == 2 (source city plus the one city joined to it)</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="72" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>TC08</t>
         </is>
       </c>
-      <c r="B19" s="46" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>getConnectedNetwork</t>
         </is>
       </c>
-      <c r="C19" s="47" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>getConnectedNetwork(City(id1, Game1, Player1)); MapEdgeRepository = [mapEdge(id1, City1&lt;-&gt;City2), mapEdge(id2, City2&lt;-&gt;City4)], all three cities owned by Player1</t>
         </is>
       </c>
-      <c r="D19" s="47" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>network.size() == 3 (city1, city2, city4)</t>
         </is>
       </c>
-      <c r="E19" s="46" t="n"/>
-      <c r="F19" s="46" t="n"/>
-      <c r="G19" s="46" t="n"/>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>network size == 3 (BFS walks through the intermediary city)</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G19" s="31" t="n"/>
     </row>
     <row r="20" ht="21" customHeight="1">
-      <c r="A20" s="46" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>TC09</t>
         </is>
       </c>
-      <c r="B20" s="46" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>findById</t>
         </is>
       </c>
-      <c r="C20" s="47" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>cityRepository = [City(id1)], findById(1)</t>
         </is>
       </c>
-      <c r="D20" s="47" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>city.getId() == 1</t>
         </is>
       </c>
-      <c r="E20" s="46" t="n"/>
-      <c r="F20" s="46" t="n"/>
-      <c r="G20" s="46" t="n"/>
-    </row>
-    <row r="21" ht="21" customHeight="1">
-      <c r="A21" s="46" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>findById(1).getId() == 1</t>
+        </is>
+      </c>
+      <c r="F20" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>TC10</t>
         </is>
       </c>
-      <c r="B21" s="46" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>findById</t>
         </is>
       </c>
-      <c r="C21" s="47" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>cityRepository = [City(id1)], findById(2)</t>
         </is>
       </c>
-      <c r="D21" s="47" t="inlineStr">
+      <c r="D21" s="33" t="inlineStr">
         <is>
           <t>City not found with id: 2 (ResourceNotFoundException)</t>
         </is>
       </c>
-      <c r="E21" s="46" t="n"/>
-      <c r="F21" s="46" t="n"/>
-      <c r="G21" s="46" t="n"/>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>ResourceNotFoundException 'City not found with id: 2'</t>
+        </is>
+      </c>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G21" s="31" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
-      <c r="A22" s="46" t="inlineStr">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>TC11</t>
         </is>
       </c>
-      <c r="B22" s="46" t="inlineStr">
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>save</t>
         </is>
       </c>
-      <c r="C22" s="47" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>save(city)</t>
         </is>
       </c>
-      <c r="D22" s="47" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>verify(cityRepository).save(city)</t>
         </is>
       </c>
-      <c r="E22" s="46" t="n"/>
-      <c r="F22" s="46" t="n"/>
-      <c r="G22" s="46" t="n"/>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>cityRepository.save(city) called once</t>
+        </is>
+      </c>
+      <c r="F22" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G22" s="31" t="n"/>
     </row>
     <row r="23" ht="63" customHeight="1">
-      <c r="A23" s="46" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>TC12</t>
         </is>
       </c>
-      <c r="B23" s="46" t="inlineStr">
+      <c r="B23" s="31" t="inlineStr">
         <is>
           <t>deductFoodFromNetwork</t>
         </is>
       </c>
-      <c r="C23" s="47" t="inlineStr">
+      <c r="C23" s="33" t="inlineStr">
         <is>
           <t>MapEdge = [mapEdge(id1, City1&lt;-&gt;City2)], all cities food=100, deductFoodFromNetwork(City(id1), 10)</t>
         </is>
       </c>
-      <c r="D23" s="47" t="inlineStr">
+      <c r="D23" s="33" t="inlineStr">
         <is>
           <t>City1.food == 95; City2.food == 95</t>
         </is>
       </c>
-      <c r="E23" s="46" t="n"/>
-      <c r="F23" s="46" t="n"/>
-      <c r="G23" s="46" t="n"/>
-    </row>
-    <row r="24" ht="84" customHeight="1">
-      <c r="A24" s="46" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>City1 100 -&gt; 95 and City2 100 -&gt; 95 (cost split evenly over the 2-city network)</t>
+        </is>
+      </c>
+      <c r="F23" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>TC13</t>
         </is>
       </c>
-      <c r="B24" s="46" t="inlineStr">
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>deductFoodFromNetwork</t>
         </is>
       </c>
-      <c r="C24" s="47" t="inlineStr">
+      <c r="C24" s="33" t="inlineStr">
         <is>
           <t>MapEdge = [mapEdge(id1, City1&lt;-&gt;City2), mapEdge(id2, City1&lt;-&gt;City3)], all food=100, deductFoodFromNetwork(City(id1), 10)</t>
         </is>
       </c>
-      <c r="D24" s="47" t="inlineStr">
+      <c r="D24" s="33" t="inlineStr">
         <is>
           <t>City1.food == 5; City2.food == 100; City3.food == 100</t>
         </is>
       </c>
-      <c r="E24" s="46" t="n"/>
-      <c r="F24" s="46" t="n"/>
-      <c r="G24" s="46" t="n"/>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>City1 == 96, City2 == 97, City3 == 97: the 10 food is split 3/3/3 over the 3-city network and the remainder 1 is charged to the triggering city, so the source is never charged the whole 10</t>
+        </is>
+      </c>
+      <c r="F24" s="31" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G24" s="31" t="inlineStr">
+        <is>
+          <t>DEF-SVC-02</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="84" customHeight="1">
-      <c r="A25" s="46" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>TC14</t>
         </is>
       </c>
-      <c r="B25" s="46" t="inlineStr">
+      <c r="B25" s="31" t="inlineStr">
         <is>
           <t>applySeasonUpkeep</t>
         </is>
       </c>
-      <c r="C25" s="47" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
         <is>
           <t>applySeasonUpkeep(1); City1(food100, soldiers25) + City3(food100, soldiers25) connected, both owned by the same player</t>
         </is>
       </c>
-      <c r="D25" s="47" t="inlineStr">
+      <c r="D25" s="33" t="inlineStr">
         <is>
           <t>City1.food == 0; City3.food == 25; totalFood == 25; soldiers unchanged; no GameEvent</t>
         </is>
       </c>
-      <c r="E25" s="46" t="n"/>
-      <c r="F25" s="46" t="n"/>
-      <c r="G25" s="46" t="n"/>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>City1 == 75, City3 == 75, no GameEvent: upkeep = total soldiers (50) deducted evenly 25/25; no city goes negative so the shortfall redistribution never runs</t>
+        </is>
+      </c>
+      <c r="F25" s="31" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G25" s="31" t="inlineStr">
+        <is>
+          <t>DEF-SVC-03</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="84" customHeight="1">
-      <c r="A26" s="46" t="inlineStr">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t>TC15</t>
         </is>
       </c>
-      <c r="B26" s="46" t="inlineStr">
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>applySeasonUpkeep</t>
         </is>
       </c>
-      <c r="C26" s="47" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
         <is>
           <t>applySeasonUpkeep(1); City1(food50, soldiers50) + City3(food100, soldiers25) connected, same owner</t>
         </is>
       </c>
-      <c r="D26" s="47" t="inlineStr">
+      <c r="D26" s="33" t="inlineStr">
         <is>
           <t>City1.food == 12; City3.food == 63; no starvation</t>
         </is>
       </c>
-      <c r="E26" s="46" t="n"/>
-      <c r="F26" s="46" t="n"/>
-      <c r="G26" s="46" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="46" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>City1 == 12 (50 - 37 - remainder 1) and City3 == 63, no GameEvent</t>
+        </is>
+      </c>
+      <c r="F26" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>TC16</t>
         </is>
       </c>
-      <c r="B27" s="46" t="inlineStr">
+      <c r="B27" s="31" t="inlineStr">
         <is>
           <t>applySeasonUpkeep</t>
         </is>
       </c>
-      <c r="C27" s="47" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>City(food50, soldiers10, player = null) only</t>
         </is>
       </c>
-      <c r="D27" s="47" t="inlineStr">
+      <c r="D27" s="33" t="inlineStr">
         <is>
           <t>food stays 50, soldiers 10; neutral city skipped; gameEventRepository.save never called</t>
         </is>
       </c>
-      <c r="E27" s="46" t="n"/>
-      <c r="F27" s="46" t="n"/>
-      <c r="G27" s="46" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="46" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>neutral city skipped: food stays 50, soldiers stay 10, gameEventRepository.save never called</t>
+        </is>
+      </c>
+      <c r="F27" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
         <is>
           <t>TC17</t>
         </is>
       </c>
-      <c r="B28" s="46" t="inlineStr">
+      <c r="B28" s="31" t="inlineStr">
         <is>
           <t>applySeasonUpkeep</t>
         </is>
       </c>
-      <c r="C28" s="47" t="inlineStr">
+      <c r="C28" s="33" t="inlineStr">
         <is>
           <t>Network CityA(food20, soldiers10) + CityB(food0, soldiers0), same owner, A listed first in findByGame_Id</t>
         </is>
       </c>
-      <c r="D28" s="47" t="inlineStr">
+      <c r="D28" s="33" t="inlineStr">
         <is>
           <t>network deducted once only - CityB is skipped via processedNetworkIds; A.food == 10, B.food == 0</t>
         </is>
       </c>
-      <c r="E28" s="46" t="n"/>
-      <c r="F28" s="46" t="n"/>
-      <c r="G28" s="46" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="46" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>network processed once: CityA 20 -&gt; 10 and CityB stays 0 (already in processedNetworkIds)</t>
+        </is>
+      </c>
+      <c r="F28" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
         <is>
           <t>TC18</t>
         </is>
       </c>
-      <c r="B29" s="46" t="inlineStr">
+      <c r="B29" s="31" t="inlineStr">
         <is>
           <t>applySeasonUpkeep</t>
         </is>
       </c>
-      <c r="C29" s="47" t="inlineStr">
+      <c r="C29" s="33" t="inlineStr">
         <is>
           <t>Single City(food=20, soldiers=20), owned</t>
         </is>
       </c>
-      <c r="D29" s="47" t="inlineStr">
+      <c r="D29" s="33" t="inlineStr">
         <is>
           <t>food == 0 exactly; soldiers unchanged; no GameEvent</t>
         </is>
       </c>
-      <c r="E29" s="46" t="n"/>
-      <c r="F29" s="46" t="n"/>
-      <c r="G29" s="46" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="46" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>single city: food 20 -&gt; 0 exactly, soldiers 20 unchanged, no GameEvent</t>
+        </is>
+      </c>
+      <c r="F29" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="31" t="inlineStr">
         <is>
           <t>TC19</t>
         </is>
       </c>
-      <c r="B30" s="46" t="inlineStr">
+      <c r="B30" s="31" t="inlineStr">
         <is>
           <t>applySeasonUpkeep</t>
         </is>
       </c>
-      <c r="C30" s="47" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
         <is>
           <t>Two-city network, food 50/50, soldiers 15/14, triggering city = City1</t>
         </is>
       </c>
-      <c r="D30" s="47" t="inlineStr">
+      <c r="D30" s="33" t="inlineStr">
         <is>
           <t>City1.food == 35; City2.food == 36</t>
         </is>
       </c>
-      <c r="E30" s="46" t="n"/>
-      <c r="F30" s="46" t="n"/>
-      <c r="G30" s="46" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="46" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>City1 == 35 and City2 == 36 (perCityCost 14, remainder 1 on the triggering city)</t>
+        </is>
+      </c>
+      <c r="F30" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="31" t="inlineStr">
         <is>
           <t>TC20</t>
         </is>
       </c>
-      <c r="B31" s="46" t="inlineStr">
+      <c r="B31" s="31" t="inlineStr">
         <is>
           <t>applySeasonUpkeep</t>
         </is>
       </c>
-      <c r="C31" s="47" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
         <is>
           <t>Two-city network, City1(food2, soldiers8), City2(food28, soldiers8), triggering = City1</t>
         </is>
       </c>
-      <c r="D31" s="47" t="inlineStr">
+      <c r="D31" s="33" t="inlineStr">
         <is>
           <t>City1.food == 0; City2.food == 14 (absorbs City1's debt)</t>
         </is>
       </c>
-      <c r="E31" s="46" t="n"/>
-      <c r="F31" s="46" t="n"/>
-      <c r="G31" s="46" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="46" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>City1 2 -&gt; 0 and its 6-point debt is absorbed by City2, which lands on 14</t>
+        </is>
+      </c>
+      <c r="F31" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G31" s="31" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t>TC21</t>
         </is>
       </c>
-      <c r="B32" s="46" t="inlineStr">
+      <c r="B32" s="31" t="inlineStr">
         <is>
           <t>applySeasonUpkeep</t>
         </is>
       </c>
-      <c r="C32" s="47" t="inlineStr">
+      <c r="C32" s="33" t="inlineStr">
         <is>
           <t>Two unconnected networks in one game: CityA(food100, soldiers50) and CityB(food10, soldiers50)</t>
         </is>
       </c>
-      <c r="D32" s="47" t="inlineStr">
+      <c r="D32" s="33" t="inlineStr">
         <is>
           <t>CityA.food == 50 no event; CityB loses 40 soldiers and one STARVATION GameEvent is saved for it</t>
         </is>
       </c>
-      <c r="E32" s="46" t="n"/>
-      <c r="F32" s="46" t="n"/>
-      <c r="G32" s="46" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="46" t="inlineStr">
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>two networks handled separately: CityA 100 -&gt; 50 with no event; CityB loses 40 soldiers (50 -&gt; 10) and exactly 1 STARVATION event with soldierImpact -40</t>
+        </is>
+      </c>
+      <c r="F32" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G32" s="31" t="n"/>
+    </row>
+    <row r="33" ht="54" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
         <is>
           <t>TC22</t>
         </is>
       </c>
-      <c r="B33" s="46" t="inlineStr">
+      <c r="B33" s="31" t="inlineStr">
         <is>
           <t>applySeasonUpkeep</t>
         </is>
       </c>
-      <c r="C33" s="47" t="inlineStr">
+      <c r="C33" s="33" t="inlineStr">
         <is>
           <t>Deficit branch: City1(food12, soldiers10) excess, City2(food3, soldiers15) deficit</t>
         </is>
       </c>
-      <c r="D33" s="47" t="inlineStr">
+      <c r="D33" s="33" t="inlineStr">
         <is>
           <t>City1.food == 0; City2.food == 0; City2.soldiers == 5; one STARVATION GameEvent saved for City2 only</t>
         </is>
       </c>
-      <c r="E33" s="46" t="n"/>
-      <c r="F33" s="46" t="n"/>
-      <c r="G33" s="46" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="46" t="inlineStr">
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>City1 12 -&gt; 0, City2 3 -&gt; 0, City2.soldiers 15 -&gt; 5 and exactly 1 STARVATION event (soldierImpact -10)</t>
+        </is>
+      </c>
+      <c r="F33" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G33" s="31" t="n"/>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="31" t="inlineStr">
         <is>
           <t>TC23</t>
         </is>
       </c>
-      <c r="B34" s="46" t="inlineStr">
+      <c r="B34" s="31" t="inlineStr">
         <is>
           <t>applySeasonUpkeep</t>
         </is>
       </c>
-      <c r="C34" s="47" t="inlineStr">
+      <c r="C34" s="33" t="inlineStr">
         <is>
           <t>Deficit branch with several deficit cities: C1(food10,s10) C2(food5,s15) C3(food0,s15)</t>
         </is>
       </c>
-      <c r="D34" s="47" t="inlineStr">
+      <c r="D34" s="33" t="inlineStr">
         <is>
           <t>shares 5 and 5 (last deficit city takes the remainder), casualties 5 each -&gt; C2.soldiers == 10, C3.soldiers == 10; sum of shares &lt;= totalExcess</t>
         </is>
       </c>
-      <c r="E34" s="46" t="n"/>
-      <c r="F34" s="46" t="n"/>
-      <c r="G34" s="46" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="46" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>totalExcess is 0 (a city only contributes excess when food &gt;= soldiers), so no share is available: City1 keeps all 10 soldiers, City2 15 -&gt; 5, City3 15 -&gt; 0, 2 STARVATION events</t>
+        </is>
+      </c>
+      <c r="F34" s="31" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G34" s="31" t="inlineStr">
+        <is>
+          <t>DEF-SVC-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="54" customHeight="1">
+      <c r="A35" s="31" t="inlineStr">
         <is>
           <t>TC24</t>
         </is>
       </c>
-      <c r="B35" s="46" t="inlineStr">
+      <c r="B35" s="31" t="inlineStr">
         <is>
           <t>applySeasonUpkeep</t>
         </is>
       </c>
-      <c r="C35" s="47" t="inlineStr">
+      <c r="C35" s="33" t="inlineStr">
         <is>
           <t>Deficit branch with zero excess: City1(food0, soldiers10), City2(food0, soldiers8)</t>
         </is>
       </c>
-      <c r="D35" s="47" t="inlineStr">
+      <c r="D35" s="33" t="inlineStr">
         <is>
           <t>both cities lose their full deficit (share == 0); soldiers 0 and 0; 2 GameEvents saved</t>
         </is>
       </c>
-      <c r="E35" s="46" t="n"/>
-      <c r="F35" s="46" t="n"/>
-      <c r="G35" s="46" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="46" t="inlineStr">
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>zero excess: both deficit cities lose their whole shortfall (soldiers 0 and 0) and 2 STARVATION events are saved</t>
+        </is>
+      </c>
+      <c r="F35" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G35" s="31" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="31" t="inlineStr">
         <is>
           <t>TC25</t>
         </is>
       </c>
-      <c r="B36" s="46" t="inlineStr">
+      <c r="B36" s="31" t="inlineStr">
         <is>
           <t>applySeasonUpkeep</t>
         </is>
       </c>
-      <c r="C36" s="47" t="inlineStr">
+      <c r="C36" s="33" t="inlineStr">
         <is>
           <t>any scenario from TC14-TC24</t>
         </is>
       </c>
-      <c r="D36" s="47" t="inlineStr">
+      <c r="D36" s="33" t="inlineStr">
         <is>
           <t>verify(cityRepository).saveAll(cities) called exactly once per applySeasonUpkeep call</t>
         </is>
       </c>
-      <c r="E36" s="46" t="n"/>
-      <c r="F36" s="46" t="n"/>
-      <c r="G36" s="46" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="46" t="inlineStr">
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>cityRepository.saveAll(cities) called exactly once for the whole upkeep</t>
+        </is>
+      </c>
+      <c r="F36" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G36" s="31" t="n"/>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="31" t="inlineStr">
         <is>
           <t>TC26</t>
         </is>
       </c>
-      <c r="B37" s="46" t="inlineStr">
+      <c r="B37" s="31" t="inlineStr">
         <is>
           <t>applySeasonUpkeep</t>
         </is>
       </c>
-      <c r="C37" s="47" t="inlineStr">
+      <c r="C37" s="33" t="inlineStr">
         <is>
           <t>cityRepository.findByGame_Id(99L) returns []</t>
         </is>
       </c>
-      <c r="D37" s="47" t="inlineStr">
+      <c r="D37" s="33" t="inlineStr">
         <is>
           <t>no exception; saveAll([]) called once; gameEventRepository.save never called</t>
         </is>
       </c>
-      <c r="E37" s="46" t="n"/>
-      <c r="F37" s="46" t="n"/>
-      <c r="G37" s="46" t="n"/>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>no exception, saveAll([]) called once, no GameEvent saved</t>
+        </is>
+      </c>
+      <c r="F37" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G37" s="31" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5364,331 +6529,394 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="4"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Project Name</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="33" t="n"/>
-      <c r="D3" s="33" t="n"/>
-      <c r="E3" s="33" t="n"/>
-      <c r="F3" s="33" t="n"/>
-      <c r="G3" s="34" t="n"/>
+      <c r="C3" s="32" t="n"/>
+      <c r="D3" s="32" t="n"/>
+      <c r="E3" s="32" t="n"/>
+      <c r="F3" s="32" t="n"/>
+      <c r="G3" s="24" t="n"/>
     </row>
     <row r="4" ht="84" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>SystemUnderTest/Class under Test</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>GameClock</t>
         </is>
       </c>
-      <c r="C4" s="33" t="n"/>
-      <c r="D4" s="33" t="n"/>
-      <c r="E4" s="33" t="n"/>
-      <c r="F4" s="33" t="n"/>
-      <c r="G4" s="34" t="n"/>
+      <c r="C4" s="32" t="n"/>
+      <c r="D4" s="32" t="n"/>
+      <c r="E4" s="32" t="n"/>
+      <c r="F4" s="32" t="n"/>
+      <c r="G4" s="24" t="n"/>
     </row>
     <row r="5" ht="35.4" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
-        <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
-        </is>
-      </c>
-      <c r="C5" s="33" t="n"/>
-      <c r="D5" s="33" t="n"/>
-      <c r="E5" s="33" t="n"/>
-      <c r="F5" s="33" t="n"/>
-      <c r="G5" s="34" t="n"/>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6" ht="21" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
+      <c r="B6" s="34" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="33" t="n"/>
-      <c r="D6" s="33" t="n"/>
-      <c r="E6" s="33" t="n"/>
-      <c r="F6" s="33" t="n"/>
-      <c r="G6" s="34" t="n"/>
+      <c r="C6" s="32" t="n"/>
+      <c r="D6" s="32" t="n"/>
+      <c r="E6" s="32" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="24" t="n"/>
     </row>
     <row r="7" ht="35.4" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>None (static methods, no mocks)</t>
         </is>
       </c>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="33" t="n"/>
-      <c r="E7" s="33" t="n"/>
-      <c r="F7" s="33" t="n"/>
-      <c r="G7" s="34" t="n"/>
+      <c r="C7" s="32" t="n"/>
+      <c r="D7" s="32" t="n"/>
+      <c r="E7" s="32" t="n"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="24" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="46" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>TestCaseID</t>
         </is>
       </c>
-      <c r="B11" s="46" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>Function Under Test</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>TestData</t>
         </is>
       </c>
-      <c r="D11" s="46" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="E11" s="46" t="inlineStr">
+      <c r="E11" s="31" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F11" s="46" t="inlineStr">
+      <c r="F11" s="31" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G11" s="46" t="inlineStr">
+      <c r="G11" s="31" t="inlineStr">
         <is>
           <t>DefectID</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="46" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>TC01</t>
         </is>
       </c>
-      <c r="B12" s="46" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="C12" s="47" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>turn = 1, 4, 5, 8, 9, 12, 13</t>
         </is>
       </c>
-      <c r="D12" s="47" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>SUMMER, SUMMER, RAINY, RAINY, WINTER, WINTER, SUMMER (12-turn cycle)</t>
         </is>
       </c>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-    </row>
-    <row r="13" ht="21" customHeight="1">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>season(1,4) SUMMER, season(5,8) RAINY, season(9,12) WINTER, season(13) SUMMER</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G12" s="31" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>TC02</t>
         </is>
       </c>
-      <c r="B13" s="46" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>isDaytime</t>
         </is>
       </c>
-      <c r="C13" s="47" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>turn = 1, 3, 2, 4</t>
         </is>
       </c>
-      <c r="D13" s="47" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>true, true, false, false</t>
         </is>
       </c>
-      <c r="E13" s="46" t="n"/>
-      <c r="F13" s="46" t="n"/>
-      <c r="G13" s="46" t="n"/>
-    </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="46" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>isDaytime: 1 true, 3 true, 2 false, 4 false</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>TC03</t>
         </is>
       </c>
-      <c r="B14" s="46" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>isSeasonEnd</t>
         </is>
       </c>
-      <c r="C14" s="47" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>turn = 4, 8, 3, 5</t>
         </is>
       </c>
-      <c r="D14" s="47" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>true, true, false, false</t>
         </is>
       </c>
-      <c r="E14" s="46" t="n"/>
-      <c r="F14" s="46" t="n"/>
-      <c r="G14" s="46" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="46" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>isSeasonEnd: 4 true, 8 true, 3 false, 5 false</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G14" s="31" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>TC04</t>
         </is>
       </c>
-      <c r="B15" s="46" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="C15" s="47" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>season(0)</t>
         </is>
       </c>
-      <c r="D15" s="47" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>WINTER - floorMod(0-1, 12) = 11</t>
         </is>
       </c>
-      <c r="E15" s="46" t="n"/>
-      <c r="F15" s="46" t="n"/>
-      <c r="G15" s="46" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="46" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>season(0) == WINTER (floorMod(0 - 1, 12) == 11)</t>
+        </is>
+      </c>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G15" s="31" t="n"/>
+    </row>
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>TC05</t>
         </is>
       </c>
-      <c r="B16" s="46" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="C16" s="47" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>season(-11)</t>
         </is>
       </c>
-      <c r="D16" s="47" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>SUMMER - Math.floorMod handles negatives (index 0)</t>
         </is>
       </c>
-      <c r="E16" s="46" t="n"/>
-      <c r="F16" s="46" t="n"/>
-      <c r="G16" s="46" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="46" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>season(-11) == SUMMER (index 0, Math.floorMod keeps negatives inside the cycle)</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G16" s="31" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>TC06</t>
         </is>
       </c>
-      <c r="B17" s="46" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>isDaytime</t>
         </is>
       </c>
-      <c r="C17" s="47" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>isDaytime(0), isDaytime(-1), isDaytime(-3)</t>
         </is>
       </c>
-      <c r="D17" s="47" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>all false: 0 % 2 == 0, and for negatives Java keeps the sign so -3 % 2 == -1, not 1</t>
         </is>
       </c>
-      <c r="E17" s="46" t="n"/>
-      <c r="F17" s="46" t="n"/>
-      <c r="G17" s="46" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="46" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>isDaytime(0), isDaytime(-1), isDaytime(-3) all false</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>TC07</t>
         </is>
       </c>
-      <c r="B18" s="46" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>isSeasonEnd</t>
         </is>
       </c>
-      <c r="C18" s="47" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>isSeasonEnd(0)</t>
         </is>
       </c>
-      <c r="D18" s="47" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>false (guard turnNumber &gt; 0)</t>
         </is>
       </c>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="46" t="n"/>
-      <c r="G18" s="46" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="46" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>isSeasonEnd(0) == false (turnNumber &gt; 0 guard)</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>TC08</t>
         </is>
       </c>
-      <c r="B19" s="46" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="C19" s="47" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>season(Integer.MAX_VALUE) / isSeasonEnd(Integer.MAX_VALUE)</t>
         </is>
       </c>
-      <c r="D19" s="47" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>no exception, no overflow in the modulo; MAX_VALUE = 2147483647 -&gt; floorMod(2147483646, 12) = 6 -&gt; RAINY</t>
         </is>
       </c>
-      <c r="E19" s="46" t="n"/>
-      <c r="F19" s="46" t="n"/>
-      <c r="G19" s="46" t="n"/>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>season(Integer.MAX_VALUE) == RAINY and isSeasonEnd(Integer.MAX_VALUE) == false; no overflow, no exception</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G19" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5714,306 +6942,361 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="4"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Project Name</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="33" t="n"/>
-      <c r="D3" s="33" t="n"/>
-      <c r="E3" s="33" t="n"/>
-      <c r="F3" s="33" t="n"/>
-      <c r="G3" s="34" t="n"/>
+      <c r="C3" s="32" t="n"/>
+      <c r="D3" s="32" t="n"/>
+      <c r="E3" s="32" t="n"/>
+      <c r="F3" s="32" t="n"/>
+      <c r="G3" s="24" t="n"/>
     </row>
     <row r="4" ht="84" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>SystemUnderTest/Class under Test</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>GameRuleService</t>
         </is>
       </c>
-      <c r="C4" s="33" t="n"/>
-      <c r="D4" s="33" t="n"/>
-      <c r="E4" s="33" t="n"/>
-      <c r="F4" s="33" t="n"/>
-      <c r="G4" s="34" t="n"/>
+      <c r="C4" s="32" t="n"/>
+      <c r="D4" s="32" t="n"/>
+      <c r="E4" s="32" t="n"/>
+      <c r="F4" s="32" t="n"/>
+      <c r="G4" s="24" t="n"/>
     </row>
     <row r="5" ht="35.4" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
-        <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
-        </is>
-      </c>
-      <c r="C5" s="33" t="n"/>
-      <c r="D5" s="33" t="n"/>
-      <c r="E5" s="33" t="n"/>
-      <c r="F5" s="33" t="n"/>
-      <c r="G5" s="34" t="n"/>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6" ht="21" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
+      <c r="B6" s="34" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="33" t="n"/>
-      <c r="D6" s="33" t="n"/>
-      <c r="E6" s="33" t="n"/>
-      <c r="F6" s="33" t="n"/>
-      <c r="G6" s="34" t="n"/>
+      <c r="C6" s="32" t="n"/>
+      <c r="D6" s="32" t="n"/>
+      <c r="E6" s="32" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="24" t="n"/>
     </row>
     <row r="7" ht="35.4" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Mock PlayerRepository, CityRepository, GameRepository</t>
         </is>
       </c>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="33" t="n"/>
-      <c r="E7" s="33" t="n"/>
-      <c r="F7" s="33" t="n"/>
-      <c r="G7" s="34" t="n"/>
+      <c r="C7" s="32" t="n"/>
+      <c r="D7" s="32" t="n"/>
+      <c r="E7" s="32" t="n"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="24" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="46" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>TestCaseID</t>
         </is>
       </c>
-      <c r="B11" s="46" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>Function Under Test</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>TestData</t>
         </is>
       </c>
-      <c r="D11" s="46" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="E11" s="46" t="inlineStr">
+      <c r="E11" s="31" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F11" s="46" t="inlineStr">
+      <c r="F11" s="31" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G11" s="46" t="inlineStr">
+      <c r="G11" s="31" t="inlineStr">
         <is>
           <t>DefectID</t>
         </is>
       </c>
     </row>
     <row r="12" ht="63" customHeight="1">
-      <c r="A12" s="46" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>TC01</t>
         </is>
       </c>
-      <c r="B12" s="46" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>checkPlayerElimination</t>
         </is>
       </c>
-      <c r="C12" s="47" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>checkPlayerElimination(player, 5); player owns no city</t>
         </is>
       </c>
-      <c r="D12" s="47" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>isAlive == false; eliminatedAtTurn == 5; playerRepository.save called</t>
         </is>
       </c>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>isAlive false, eliminatedAtTurn == 5, playerRepository.save called once</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G12" s="31" t="n"/>
     </row>
     <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>TC02</t>
         </is>
       </c>
-      <c r="B13" s="46" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>checkPlayerElimination</t>
         </is>
       </c>
-      <c r="C13" s="47" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>checkPlayerElimination(player, 5); player still owns 1 city</t>
         </is>
       </c>
-      <c r="D13" s="47" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>isAlive stays true; save never called</t>
         </is>
       </c>
-      <c r="E13" s="46" t="n"/>
-      <c r="F13" s="46" t="n"/>
-      <c r="G13" s="46" t="n"/>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>isAlive stays true, playerRepository.save never called</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="n"/>
     </row>
     <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="46" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>TC03</t>
         </is>
       </c>
-      <c r="B14" s="46" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>checkWinCondition</t>
         </is>
       </c>
-      <c r="C14" s="47" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>checkWinCondition(game IN_PROGRESS) with only 1 alive player</t>
         </is>
       </c>
-      <c r="D14" s="47" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>status == FINISHED; winner set; gameRepository.save called</t>
         </is>
       </c>
-      <c r="E14" s="46" t="n"/>
-      <c r="F14" s="46" t="n"/>
-      <c r="G14" s="46" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="46" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>status FINISHED, winner is the only alive player, gameRepository.save called</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G14" s="31" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>TC04</t>
         </is>
       </c>
-      <c r="B15" s="46" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>checkWinCondition</t>
         </is>
       </c>
-      <c r="C15" s="47" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>only 0 alive players left, game IN_PROGRESS</t>
         </is>
       </c>
-      <c r="D15" s="47" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>status == FINISHED; winner == null; gameRepository.save called</t>
         </is>
       </c>
-      <c r="E15" s="46" t="n"/>
-      <c r="F15" s="46" t="n"/>
-      <c r="G15" s="46" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="46" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>status FINISHED with winner == null, gameRepository.save called</t>
+        </is>
+      </c>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G15" s="31" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>TC05</t>
         </is>
       </c>
-      <c r="B16" s="46" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>checkWinCondition</t>
         </is>
       </c>
-      <c r="C16" s="47" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>2 or more alive players, game IN_PROGRESS</t>
         </is>
       </c>
-      <c r="D16" s="47" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>no change: status stays IN_PROGRESS; gameRepository.save never called</t>
         </is>
       </c>
-      <c r="E16" s="46" t="n"/>
-      <c r="F16" s="46" t="n"/>
-      <c r="G16" s="46" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="46" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>status stays IN_PROGRESS, no save</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G16" s="31" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>TC06</t>
         </is>
       </c>
-      <c r="B17" s="46" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>checkWinCondition</t>
         </is>
       </c>
-      <c r="C17" s="47" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>game in WAITING / PLACEMENT / MARSHAL_SELECTION with &lt;= 1 alive player</t>
         </is>
       </c>
-      <c r="D17" s="47" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>no change - the phase guard blocks finishing</t>
         </is>
       </c>
-      <c r="E17" s="46" t="n"/>
-      <c r="F17" s="46" t="n"/>
-      <c r="G17" s="46" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="46" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>WAITING, PLACEMENT and MARSHAL_SELECTION all unchanged, no save (phase guard)</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>TC07</t>
         </is>
       </c>
-      <c r="B18" s="46" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>checkPlayerElimination</t>
         </is>
       </c>
-      <c r="C18" s="47" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>called twice on an already-eliminated player owning no city</t>
         </is>
       </c>
-      <c r="D18" s="47" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>second call still sets isAlive false / eliminatedAtTurn and calls save again (no idempotency guard)</t>
         </is>
       </c>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="46" t="n"/>
-      <c r="G18" s="46" t="n"/>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>no idempotency guard: the second call rewrites eliminatedAtTurn to 7 and saves once more</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G18" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6039,406 +7322,493 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="4"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Project Name</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="33" t="n"/>
-      <c r="D3" s="33" t="n"/>
-      <c r="E3" s="33" t="n"/>
-      <c r="F3" s="33" t="n"/>
-      <c r="G3" s="34" t="n"/>
+      <c r="C3" s="32" t="n"/>
+      <c r="D3" s="32" t="n"/>
+      <c r="E3" s="32" t="n"/>
+      <c r="F3" s="32" t="n"/>
+      <c r="G3" s="24" t="n"/>
     </row>
     <row r="4" ht="84" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>SystemUnderTest/Class under Test</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>GameService</t>
         </is>
       </c>
-      <c r="C4" s="33" t="n"/>
-      <c r="D4" s="33" t="n"/>
-      <c r="E4" s="33" t="n"/>
-      <c r="F4" s="33" t="n"/>
-      <c r="G4" s="34" t="n"/>
+      <c r="C4" s="32" t="n"/>
+      <c r="D4" s="32" t="n"/>
+      <c r="E4" s="32" t="n"/>
+      <c r="F4" s="32" t="n"/>
+      <c r="G4" s="24" t="n"/>
     </row>
     <row r="5" ht="35.4" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
-        <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
-        </is>
-      </c>
-      <c r="C5" s="33" t="n"/>
-      <c r="D5" s="33" t="n"/>
-      <c r="E5" s="33" t="n"/>
-      <c r="F5" s="33" t="n"/>
-      <c r="G5" s="34" t="n"/>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6" ht="21" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
+      <c r="B6" s="34" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="33" t="n"/>
-      <c r="D6" s="33" t="n"/>
-      <c r="E6" s="33" t="n"/>
-      <c r="F6" s="33" t="n"/>
-      <c r="G6" s="34" t="n"/>
+      <c r="C6" s="32" t="n"/>
+      <c r="D6" s="32" t="n"/>
+      <c r="E6" s="32" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="24" t="n"/>
     </row>
     <row r="7" ht="35.4" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Mock GameRepository, PlayerRepository, MarshalService, CityRepository, MapEdgeRepository, MarshalDraftService</t>
         </is>
       </c>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="33" t="n"/>
-      <c r="E7" s="33" t="n"/>
-      <c r="F7" s="33" t="n"/>
-      <c r="G7" s="34" t="n"/>
+      <c r="C7" s="32" t="n"/>
+      <c r="D7" s="32" t="n"/>
+      <c r="E7" s="32" t="n"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="24" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="46" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>TestCaseID</t>
         </is>
       </c>
-      <c r="B11" s="46" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>Function Under Test</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>TestData</t>
         </is>
       </c>
-      <c r="D11" s="46" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="E11" s="46" t="inlineStr">
+      <c r="E11" s="31" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F11" s="46" t="inlineStr">
+      <c r="F11" s="31" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G11" s="46" t="inlineStr">
+      <c r="G11" s="31" t="inlineStr">
         <is>
           <t>DefectID</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="46" t="inlineStr">
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>TC01</t>
         </is>
       </c>
-      <c r="B12" s="46" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>createGame</t>
         </is>
       </c>
-      <c r="C12" s="47" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>createGame(); gameRepository.save returns Game(roomCode TEST12, WAITING)</t>
         </is>
       </c>
-      <c r="D12" s="47" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>game not null; status == WAITING; currentTurnNumber == 0; 6-character roomCode; save called</t>
         </is>
       </c>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>game not null, status WAITING, currentTurnNumber 0, roomCode length 6, gameRepository.save called</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G12" s="31" t="n"/>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>TC02</t>
         </is>
       </c>
-      <c r="B13" s="46" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>addPlayer</t>
         </is>
       </c>
-      <c r="C13" s="47" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>addPlayer(1L, 'Player1') on a WAITING game with &lt; 7 players</t>
         </is>
       </c>
-      <c r="D13" s="47" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>player saved with name 'Player1', isAlive true, rerollCount 0 and non-null PlayerStats</t>
         </is>
       </c>
-      <c r="E13" s="46" t="n"/>
-      <c r="F13" s="46" t="n"/>
-      <c r="G13" s="46" t="n"/>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>player saved with name 'Player1', isAlive true, rerollCount 0 and a non-null PlayerStats</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="n"/>
     </row>
     <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="46" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>TC03</t>
         </is>
       </c>
-      <c r="B14" s="46" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>addPlayer</t>
         </is>
       </c>
-      <c r="C14" s="47" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>addPlayer(1L, 'Player8'); countByGame_Id(1L) = 7</t>
         </is>
       </c>
-      <c r="D14" s="47" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'A game can have at most 7 players'</t>
         </is>
       </c>
-      <c r="E14" s="46" t="n"/>
-      <c r="F14" s="46" t="n"/>
-      <c r="G14" s="46" t="n"/>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'A game can have at most 7 players'</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G14" s="31" t="n"/>
     </row>
     <row r="15" ht="63" customHeight="1">
-      <c r="A15" s="46" t="inlineStr">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>TC04</t>
         </is>
       </c>
-      <c r="B15" s="46" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>addPlayer</t>
         </is>
       </c>
-      <c r="C15" s="47" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>addPlayer(1L, 'Player2') while game.status = IN_PROGRESS</t>
         </is>
       </c>
-      <c r="D15" s="47" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'Game is no longer accepting players'</t>
         </is>
       </c>
-      <c r="E15" s="46" t="n"/>
-      <c r="F15" s="46" t="n"/>
-      <c r="G15" s="46" t="n"/>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'Game is no longer accepting players'</t>
+        </is>
+      </c>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G15" s="31" t="n"/>
     </row>
     <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="46" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>TC05</t>
         </is>
       </c>
-      <c r="B16" s="46" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>addPlayer</t>
         </is>
       </c>
-      <c r="C16" s="47" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>addPlayer(1L, '   ') on a WAITING game</t>
         </is>
       </c>
-      <c r="D16" s="47" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'Player name is required'</t>
         </is>
       </c>
-      <c r="E16" s="46" t="n"/>
-      <c r="F16" s="46" t="n"/>
-      <c r="G16" s="46" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="46" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'Player name is required'</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G16" s="31" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>TC06</t>
         </is>
       </c>
-      <c r="B17" s="46" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>startGame</t>
         </is>
       </c>
-      <c r="C17" s="47" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>startGame(1L) with only 1 player in the game</t>
         </is>
       </c>
-      <c r="D17" s="47" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'A game requires between 2 and 7 players'</t>
         </is>
       </c>
-      <c r="E17" s="46" t="n"/>
-      <c r="F17" s="46" t="n"/>
-      <c r="G17" s="46" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="46" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'A game requires between 2 and 7 players'</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>TC07</t>
         </is>
       </c>
-      <c r="B18" s="46" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>startGame</t>
         </is>
       </c>
-      <c r="C18" s="47" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>startGame(1L); WAITING game with 2 players, ensureDefaultMarshals returns 3</t>
         </is>
       </c>
-      <c r="D18" s="47" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>status == MARSHAL_SELECTION; currentTurnNumber == 0; 6 cities and cycle MapEdges generated; game saved; prepareNextPlayer(1L) called</t>
         </is>
       </c>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="46" t="n"/>
-      <c r="G18" s="46" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="46" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>status MARSHAL_SELECTION with currentTurnNumber 0, 6 cities saved, at least 6 MapEdges saved through saveAll, game saved and prepareNextPlayer(1L) called</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>TC08</t>
         </is>
       </c>
-      <c r="B19" s="46" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>startGame</t>
         </is>
       </c>
-      <c r="C19" s="47" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>startGame(1L) when game.status is already MARSHAL_SELECTION</t>
         </is>
       </c>
-      <c r="D19" s="47" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'Game has already started'</t>
         </is>
       </c>
-      <c r="E19" s="46" t="n"/>
-      <c r="F19" s="46" t="n"/>
-      <c r="G19" s="46" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="46" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'Game has already started'</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>TC09</t>
         </is>
       </c>
-      <c r="B20" s="46" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>startGame</t>
         </is>
       </c>
-      <c r="C20" s="47" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>startGame(1L) with 2 players but marshalRepository returns only 1 Marshal</t>
         </is>
       </c>
-      <c r="D20" s="47" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'Not enough marshal records are configured'</t>
         </is>
       </c>
-      <c r="E20" s="46" t="n"/>
-      <c r="F20" s="46" t="n"/>
-      <c r="G20" s="46" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="46" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'Not enough marshal records are configured'</t>
+        </is>
+      </c>
+      <c r="F20" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>TC10</t>
         </is>
       </c>
-      <c r="B21" s="46" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>findByRoomCode</t>
         </is>
       </c>
-      <c r="C21" s="47" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>findByRoomCode('NOPE'), repository has no such room code</t>
         </is>
       </c>
-      <c r="D21" s="47" t="inlineStr">
+      <c r="D21" s="33" t="inlineStr">
         <is>
           <t>Game not found with room code: NOPE (ResourceNotFoundException)</t>
         </is>
       </c>
-      <c r="E21" s="46" t="n"/>
-      <c r="F21" s="46" t="n"/>
-      <c r="G21" s="46" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="46" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>ResourceNotFoundException 'Game not found with room code: NOPE'</t>
+        </is>
+      </c>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>TC11</t>
         </is>
       </c>
-      <c r="B22" s="46" t="inlineStr">
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>findPlayers</t>
         </is>
       </c>
-      <c r="C22" s="47" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>findPlayers(1L) with 3 players in the game</t>
         </is>
       </c>
-      <c r="D22" s="47" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>returns the 3 players ordered by id</t>
         </is>
       </c>
-      <c r="E22" s="46" t="n"/>
-      <c r="F22" s="46" t="n"/>
-      <c r="G22" s="46" t="n"/>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>findPlayers(1L) returns the 3 players in id order</t>
+        </is>
+      </c>
+      <c r="F22" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G22" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6464,506 +7834,629 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="4"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Project Name</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="33" t="n"/>
-      <c r="D3" s="33" t="n"/>
-      <c r="E3" s="33" t="n"/>
-      <c r="F3" s="33" t="n"/>
-      <c r="G3" s="34" t="n"/>
+      <c r="C3" s="32" t="n"/>
+      <c r="D3" s="32" t="n"/>
+      <c r="E3" s="32" t="n"/>
+      <c r="F3" s="32" t="n"/>
+      <c r="G3" s="24" t="n"/>
     </row>
     <row r="4" ht="84" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>SystemUnderTest/Class under Test</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>MarshalDraftService</t>
         </is>
       </c>
-      <c r="C4" s="33" t="n"/>
-      <c r="D4" s="33" t="n"/>
-      <c r="E4" s="33" t="n"/>
-      <c r="F4" s="33" t="n"/>
-      <c r="G4" s="34" t="n"/>
+      <c r="C4" s="32" t="n"/>
+      <c r="D4" s="32" t="n"/>
+      <c r="E4" s="32" t="n"/>
+      <c r="F4" s="32" t="n"/>
+      <c r="G4" s="24" t="n"/>
     </row>
     <row r="5" ht="35.4" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
-        <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
-        </is>
-      </c>
-      <c r="C5" s="33" t="n"/>
-      <c r="D5" s="33" t="n"/>
-      <c r="E5" s="33" t="n"/>
-      <c r="F5" s="33" t="n"/>
-      <c r="G5" s="34" t="n"/>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6" ht="21" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
+      <c r="B6" s="34" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="33" t="n"/>
-      <c r="D6" s="33" t="n"/>
-      <c r="E6" s="33" t="n"/>
-      <c r="F6" s="33" t="n"/>
-      <c r="G6" s="34" t="n"/>
+      <c r="C6" s="32" t="n"/>
+      <c r="D6" s="32" t="n"/>
+      <c r="E6" s="32" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="24" t="n"/>
     </row>
     <row r="7" ht="35.4" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Mock GameRepository, PlayerRepository, MarshalRepository, MarshalCandidateRepository</t>
         </is>
       </c>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="33" t="n"/>
-      <c r="E7" s="33" t="n"/>
-      <c r="F7" s="33" t="n"/>
-      <c r="G7" s="34" t="n"/>
+      <c r="C7" s="32" t="n"/>
+      <c r="D7" s="32" t="n"/>
+      <c r="E7" s="32" t="n"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="24" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="46" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>TestCaseID</t>
         </is>
       </c>
-      <c r="B11" s="46" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>Function Under Test</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>TestData</t>
         </is>
       </c>
-      <c r="D11" s="46" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="E11" s="46" t="inlineStr">
+      <c r="E11" s="31" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F11" s="46" t="inlineStr">
+      <c r="F11" s="31" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G11" s="46" t="inlineStr">
+      <c r="G11" s="31" t="inlineStr">
         <is>
           <t>DefectID</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="21" customHeight="1">
-      <c r="A12" s="46" t="inlineStr">
+    <row r="12" ht="72" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>TC01</t>
         </is>
       </c>
-      <c r="B12" s="46" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>prepareNextPlayer</t>
         </is>
       </c>
-      <c r="C12" s="47" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>prepareNextPlayer(1L); game MARSHAL_SELECTION, players [P1(marshal null), P2(null)], marshalRepository.findAll = 5 Marshals, no candidates yet</t>
         </is>
       </c>
-      <c r="D12" s="47" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>3 MarshalCandidate saved with slotNumber 1-3, isSelected false, all for P1</t>
         </is>
       </c>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-    </row>
-    <row r="13" ht="21" customHeight="1">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>3 MarshalCandidate saved for player 1 with slotNumber 1, 2, 3 and isSelected false</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G12" s="31" t="n"/>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>TC02</t>
         </is>
       </c>
-      <c r="B13" s="46" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>prepareNextPlayer</t>
         </is>
       </c>
-      <c r="C13" s="47" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>P1 already has 3 candidates saved</t>
         </is>
       </c>
-      <c r="D13" s="47" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>returns the existing 3 candidates; marshalRepository.findAll and shuffle NOT called</t>
         </is>
       </c>
-      <c r="E13" s="46" t="n"/>
-      <c r="F13" s="46" t="n"/>
-      <c r="G13" s="46" t="n"/>
-    </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="46" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>the existing 3 candidates are returned; marshalRepository.findAll and candidateRepository.save never called</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>TC03</t>
         </is>
       </c>
-      <c r="B14" s="46" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>prepareNextPlayer</t>
         </is>
       </c>
-      <c r="C14" s="47" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>all players already have a marshal</t>
         </is>
       </c>
-      <c r="D14" s="47" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>returns []; game.status == PLACEMENT; gameRepository.save called</t>
         </is>
       </c>
-      <c r="E14" s="46" t="n"/>
-      <c r="F14" s="46" t="n"/>
-      <c r="G14" s="46" t="n"/>
-    </row>
-    <row r="15" ht="21" customHeight="1">
-      <c r="A15" s="46" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>empty list returned, game moved to PLACEMENT and saved</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G14" s="31" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>TC04</t>
         </is>
       </c>
-      <c r="B15" s="46" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>prepareNextPlayer</t>
         </is>
       </c>
-      <c r="C15" s="47" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>game.status = IN_PROGRESS</t>
         </is>
       </c>
-      <c r="D15" s="47" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'Game is not in marshal selection'</t>
         </is>
       </c>
-      <c r="E15" s="46" t="n"/>
-      <c r="F15" s="46" t="n"/>
-      <c r="G15" s="46" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="46" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'Game is not in marshal selection'</t>
+        </is>
+      </c>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G15" s="31" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>TC05</t>
         </is>
       </c>
-      <c r="B16" s="46" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>prepareNextPlayer</t>
         </is>
       </c>
-      <c r="C16" s="47" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>gameRepository.findById(99L) empty</t>
         </is>
       </c>
-      <c r="D16" s="47" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>throws ResourceNotFoundException 'Game not found with id: 99'</t>
         </is>
       </c>
-      <c r="E16" s="46" t="n"/>
-      <c r="F16" s="46" t="n"/>
-      <c r="G16" s="46" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="46" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>ResourceNotFoundException 'Game not found with id: 99'</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G16" s="31" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>TC06</t>
         </is>
       </c>
-      <c r="B17" s="46" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>prepareNextPlayer</t>
         </is>
       </c>
-      <c r="C17" s="47" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>all remaining Marshals already taken by other players (pool empty)</t>
         </is>
       </c>
-      <c r="D17" s="47" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'No marshals are available for this draft'</t>
         </is>
       </c>
-      <c r="E17" s="46" t="n"/>
-      <c r="F17" s="46" t="n"/>
-      <c r="G17" s="46" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="46" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'No marshals are available for this draft'</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>TC07</t>
         </is>
       </c>
-      <c r="B18" s="46" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>prepareNextPlayer</t>
         </is>
       </c>
-      <c r="C18" s="47" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>used marshal ids = [1,2] out of 4 Marshals</t>
         </is>
       </c>
-      <c r="D18" s="47" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>the 3 offered candidates never include Marshal id 1 or 2</t>
         </is>
       </c>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="46" t="n"/>
-      <c r="G18" s="46" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="46" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>only 2 candidates are offered, not 3: the pool is min(3, remaining marshals) and 2 of the 4 marshals are already held. The exclusion itself holds - neither offer is Marshal id 1 or 2</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G18" s="31" t="inlineStr">
+        <is>
+          <t>DEF-SVC-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>TC08</t>
         </is>
       </c>
-      <c r="B19" s="46" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>reroll</t>
         </is>
       </c>
-      <c r="C19" s="47" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>P1 rerollCount 0, 3 candidates saved</t>
         </is>
       </c>
-      <c r="D19" s="47" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>returns the candidate at slot 2 (nextSlot = rerollCount + 2); rerollCount becomes 1; player saved</t>
         </is>
       </c>
-      <c r="E19" s="46" t="n"/>
-      <c r="F19" s="46" t="n"/>
-      <c r="G19" s="46" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="46" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>the slot-2 candidate is returned, rerollCount 0 -&gt; 1 and the player is saved</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>TC09</t>
         </is>
       </c>
-      <c r="B20" s="46" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>reroll</t>
         </is>
       </c>
-      <c r="C20" s="47" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>P1 rerollCount 2 with 3 candidates</t>
         </is>
       </c>
-      <c r="D20" s="47" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'No rerolls remain'</t>
         </is>
       </c>
-      <c r="E20" s="46" t="n"/>
-      <c r="F20" s="46" t="n"/>
-      <c r="G20" s="46" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="46" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'No rerolls remain'</t>
+        </is>
+      </c>
+      <c r="F20" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>TC10</t>
         </is>
       </c>
-      <c r="B21" s="46" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>reroll</t>
         </is>
       </c>
-      <c r="C21" s="47" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>P2 is called while P1 has not picked a marshal yet</t>
         </is>
       </c>
-      <c r="D21" s="47" t="inlineStr">
+      <c r="D21" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'It is not this player's draft turn'</t>
         </is>
       </c>
-      <c r="E21" s="46" t="n"/>
-      <c r="F21" s="46" t="n"/>
-      <c r="G21" s="46" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="46" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'It is not this player's draft turn'</t>
+        </is>
+      </c>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>TC11</t>
         </is>
       </c>
-      <c r="B22" s="46" t="inlineStr">
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>reroll</t>
         </is>
       </c>
-      <c r="C22" s="47" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>game.status != MARSHAL_SELECTION</t>
         </is>
       </c>
-      <c r="D22" s="47" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'Game is not in marshal selection'</t>
         </is>
       </c>
-      <c r="E22" s="46" t="n"/>
-      <c r="F22" s="46" t="n"/>
-      <c r="G22" s="46" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="46" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'Game is not in marshal selection'</t>
+        </is>
+      </c>
+      <c r="F22" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="72" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>TC12</t>
         </is>
       </c>
-      <c r="B23" s="46" t="inlineStr">
+      <c r="B23" s="31" t="inlineStr">
         <is>
           <t>selectCurrentCandidate</t>
         </is>
       </c>
-      <c r="C23" s="47" t="inlineStr">
+      <c r="C23" s="33" t="inlineStr">
         <is>
           <t>P1 rerollCount 0, candidates [A,B,C]</t>
         </is>
       </c>
-      <c r="D23" s="47" t="inlineStr">
+      <c r="D23" s="33" t="inlineStr">
         <is>
           <t>A.isSelected == true and saved; P1.marshal = A; prepareNextPlayer called for the next player</t>
         </is>
       </c>
-      <c r="E23" s="46" t="n"/>
-      <c r="F23" s="46" t="n"/>
-      <c r="G23" s="46" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="46" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>candidate A isSelected true (B still false), P1.marshal = A, A saved and the next player's hand is loaded (findByPlayer_IdOrderBySlotNumber(2L))</t>
+        </is>
+      </c>
+      <c r="F23" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>TC13</t>
         </is>
       </c>
-      <c r="B24" s="46" t="inlineStr">
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>selectCurrentCandidate</t>
         </is>
       </c>
-      <c r="C24" s="47" t="inlineStr">
+      <c r="C24" s="33" t="inlineStr">
         <is>
           <t>P1 rerollCount 1, candidates [A,B,C]</t>
         </is>
       </c>
-      <c r="D24" s="47" t="inlineStr">
+      <c r="D24" s="33" t="inlineStr">
         <is>
           <t>candidates.get(slot-1) with slot = min(rerollCount+1, size) = 2 -&gt; B is selected</t>
         </is>
       </c>
-      <c r="E24" s="46" t="n"/>
-      <c r="F24" s="46" t="n"/>
-      <c r="G24" s="46" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="46" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>with rerollCount 1 the slot-2 candidate B is the one marked selected</t>
+        </is>
+      </c>
+      <c r="F24" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>TC14</t>
         </is>
       </c>
-      <c r="B25" s="46" t="inlineStr">
+      <c r="B25" s="31" t="inlineStr">
         <is>
           <t>selectCurrentCandidate</t>
         </is>
       </c>
-      <c r="C25" s="47" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
         <is>
           <t>last player without a marshal picks</t>
         </is>
       </c>
-      <c r="D25" s="47" t="inlineStr">
+      <c r="D25" s="33" t="inlineStr">
         <is>
           <t>all players have a marshal -&gt; game.status == PLACEMENT and game saved</t>
         </is>
       </c>
-      <c r="E25" s="46" t="n"/>
-      <c r="F25" s="46" t="n"/>
-      <c r="G25" s="46" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="46" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>last pick in the draft: game status PLACEMENT and saved, no extra game lookup</t>
+        </is>
+      </c>
+      <c r="F25" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t>TC15</t>
         </is>
       </c>
-      <c r="B26" s="46" t="inlineStr">
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>selectCurrentCandidate</t>
         </is>
       </c>
-      <c r="C26" s="47" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
         <is>
           <t>candidateRepository.findByPlayer_IdOrderBySlotNumber(playerId) returns []</t>
         </is>
       </c>
-      <c r="D26" s="47" t="inlineStr">
+      <c r="D26" s="33" t="inlineStr">
         <is>
           <t>throws BusinessLogicException 'No marshal candidates are available'</t>
         </is>
       </c>
-      <c r="E26" s="46" t="n"/>
-      <c r="F26" s="46" t="n"/>
-      <c r="G26" s="46" t="n"/>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>BusinessLogicException 'No marshal candidates are available'; no candidate saved</t>
+        </is>
+      </c>
+      <c r="F26" s="31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G26" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
